--- a/public/exports/29189447.xlsx
+++ b/public/exports/29189447.xlsx
@@ -831,7 +831,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5334804</t>
+          <t xml:space="preserve">265333, 265334</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="F17">
-        <v>1813</v>
+        <v>418</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5334883</t>
+          <t xml:space="preserve">265751, 265752</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="F18">
-        <v>1071</v>
+        <v>939</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5334983</t>
+          <t xml:space="preserve">267924, 267925, 267926</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F19">
-        <v>354</v>
+        <v>600</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -981,16 +981,16 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5335507</t>
+          <t xml:space="preserve">270089</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F20">
-        <v>412</v>
+        <v>2052</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1031,16 +1031,16 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5336438</t>
+          <t xml:space="preserve">270575</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F21">
-        <v>2726</v>
+        <v>2562</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1081,16 +1081,16 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">719610, 2398678</t>
+          <t xml:space="preserve">271115, 271116</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F22">
-        <v>591</v>
+        <v>6192</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1131,16 +1131,16 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">719610, 2398678</t>
+          <t xml:space="preserve">272010</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F23">
-        <v>398</v>
+        <v>1846</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1181,16 +1181,16 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">719616, 5339534</t>
+          <t xml:space="preserve">272010, 272011</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F24">
-        <v>671</v>
+        <v>1658</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">719728, 5340331</t>
+          <t xml:space="preserve">5334804</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="F25">
-        <v>268</v>
+        <v>1813</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">719739, 5336599</t>
+          <t xml:space="preserve">5334883</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1290,7 +1290,7 @@
         </is>
       </c>
       <c r="F26">
-        <v>325</v>
+        <v>1071</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1331,16 +1331,16 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">719742, 9386046</t>
+          <t xml:space="preserve">5334983</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F27">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">719759, 2391621</t>
+          <t xml:space="preserve">5335507</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F28">
-        <v>3125</v>
+        <v>412</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1431,16 +1431,16 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">719761, 2391872</t>
+          <t xml:space="preserve">719610, 2398678</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F29">
-        <v>328</v>
+        <v>591</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1481,16 +1481,16 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">719772, 2409825</t>
+          <t xml:space="preserve">719610, 2398678</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F30">
-        <v>2306</v>
+        <v>398</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1531,30 +1531,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408102</t>
+          <t xml:space="preserve">719728, 5340331</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F31">
-        <v>489</v>
+        <v>268</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">200031720</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-05-25</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1581,30 +1581,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">7226325</t>
+          <t xml:space="preserve">719739, 5336599</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F32">
-        <v>439</v>
+        <v>325</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">200042618</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-08</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">5335077</t>
+          <t xml:space="preserve">719761, 2391872</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1640,26 +1640,26 @@
         </is>
       </c>
       <c r="F33">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311218750</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-20</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2399431</t>
+          <t xml:space="preserve">5336438</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1690,26 +1690,26 @@
         </is>
       </c>
       <c r="F34">
-        <v>400</v>
+        <v>2726</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219459</t>
+          <t xml:space="preserve">200020593</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-22</t>
+          <t xml:space="preserve">2019-09-17</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -1731,35 +1731,35 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2399431</t>
+          <t xml:space="preserve">2408102</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F35">
-        <v>326</v>
+        <v>489</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219459</t>
+          <t xml:space="preserve">200031720</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-22</t>
+          <t xml:space="preserve">2020-05-25</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -1781,35 +1781,35 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2393544</t>
+          <t xml:space="preserve">7226325</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F36">
-        <v>464</v>
+        <v>439</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219966</t>
+          <t xml:space="preserve">200042618</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-29</t>
+          <t xml:space="preserve">2020-12-08</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -1831,35 +1831,35 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2393544</t>
+          <t xml:space="preserve">719616, 5339534</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F37">
-        <v>464</v>
+        <v>671</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219966</t>
+          <t xml:space="preserve">200047054</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-29</t>
+          <t xml:space="preserve">2021-03-21</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -1881,25 +1881,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2393544</t>
+          <t xml:space="preserve">5335077</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F38">
-        <v>464</v>
+        <v>310</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219966</t>
+          <t xml:space="preserve">311218750</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-29</t>
+          <t xml:space="preserve">2026-12-20</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1931,25 +1931,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2393544</t>
+          <t xml:space="preserve">2399431</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F39">
-        <v>464</v>
+        <v>400</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219966</t>
+          <t xml:space="preserve">311219459</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-29</t>
+          <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -1981,25 +1981,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">5334816</t>
+          <t xml:space="preserve">2399431</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F40">
-        <v>1192</v>
+        <v>326</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311220229</t>
+          <t xml:space="preserve">311219459</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-02</t>
+          <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2031,25 +2031,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">5335410</t>
+          <t xml:space="preserve">2393544</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F41">
-        <v>288</v>
+        <v>464</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311220230</t>
+          <t xml:space="preserve">311219966</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-02</t>
+          <t xml:space="preserve">2026-12-29</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2081,25 +2081,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">5336543</t>
+          <t xml:space="preserve">2393544</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F42">
-        <v>606</v>
+        <v>464</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311220222</t>
+          <t xml:space="preserve">311219966</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-02</t>
+          <t xml:space="preserve">2026-12-29</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2131,25 +2131,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">8366959</t>
+          <t xml:space="preserve">2393544</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F43">
-        <v>509</v>
+        <v>464</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311220673</t>
+          <t xml:space="preserve">311219966</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-04</t>
+          <t xml:space="preserve">2026-12-29</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2181,25 +2181,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">265751, 265752</t>
+          <t xml:space="preserve">2393544</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F44">
-        <v>939</v>
+        <v>464</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311222478</t>
+          <t xml:space="preserve">311219966</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-13</t>
+          <t xml:space="preserve">2026-12-29</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">100078242</t>
+          <t xml:space="preserve">5334816</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2240,16 +2240,16 @@
         </is>
       </c>
       <c r="F45">
-        <v>6249</v>
+        <v>1192</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225362</t>
+          <t xml:space="preserve">311220229</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-30</t>
+          <t xml:space="preserve">2027-01-02</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">8033723</t>
+          <t xml:space="preserve">5336543</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2290,16 +2290,16 @@
         </is>
       </c>
       <c r="F46">
-        <v>2314</v>
+        <v>606</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311229616</t>
+          <t xml:space="preserve">311220222</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-21</t>
+          <t xml:space="preserve">2027-01-02</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">5340673</t>
+          <t xml:space="preserve">8366959</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2340,16 +2340,16 @@
         </is>
       </c>
       <c r="F47">
-        <v>1017</v>
+        <v>509</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311233036</t>
+          <t xml:space="preserve">311220673</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-09</t>
+          <t xml:space="preserve">2027-01-04</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">5335611</t>
+          <t xml:space="preserve">100078242</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2390,16 +2390,16 @@
         </is>
       </c>
       <c r="F48">
-        <v>1170</v>
+        <v>6249</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311233787</t>
+          <t xml:space="preserve">311225362</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-13</t>
+          <t xml:space="preserve">2027-01-30</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">5336544</t>
+          <t xml:space="preserve">8033723</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2440,16 +2440,16 @@
         </is>
       </c>
       <c r="F49">
-        <v>730</v>
+        <v>2314</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311233788</t>
+          <t xml:space="preserve">311229616</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-13</t>
+          <t xml:space="preserve">2027-02-21</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">270089</t>
+          <t xml:space="preserve">5340673</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2490,16 +2490,16 @@
         </is>
       </c>
       <c r="F50">
-        <v>2052</v>
+        <v>1017</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234340</t>
+          <t xml:space="preserve">311233036</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-15</t>
+          <t xml:space="preserve">2027-03-09</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">5335507</t>
+          <t xml:space="preserve">5335611</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2540,16 +2540,16 @@
         </is>
       </c>
       <c r="F51">
-        <v>303</v>
+        <v>1170</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234423</t>
+          <t xml:space="preserve">311233787</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-15</t>
+          <t xml:space="preserve">2027-03-13</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2581,25 +2581,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">5335507</t>
+          <t xml:space="preserve">5336544</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F52">
-        <v>412</v>
+        <v>730</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234425</t>
+          <t xml:space="preserve">311233788</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-15</t>
+          <t xml:space="preserve">2027-03-13</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2636,15 +2636,15 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F53">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234425</t>
+          <t xml:space="preserve">311234423</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2686,15 +2686,15 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F54">
-        <v>1244</v>
+        <v>412</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234435</t>
+          <t xml:space="preserve">311234425</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F55">
@@ -2781,20 +2781,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">5340827</t>
+          <t xml:space="preserve">5335507</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F56">
-        <v>1983</v>
+        <v>1244</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234426</t>
+          <t xml:space="preserve">311234435</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2831,25 +2831,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">7573379</t>
+          <t xml:space="preserve">5335507</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F57">
-        <v>512</v>
+        <v>306</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311236497</t>
+          <t xml:space="preserve">311234425</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-24</t>
+          <t xml:space="preserve">2027-03-15</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2881,25 +2881,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">7573379</t>
+          <t xml:space="preserve">5340827</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F58">
-        <v>512</v>
+        <v>1983</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311236497</t>
+          <t xml:space="preserve">311234426</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-24</t>
+          <t xml:space="preserve">2027-03-15</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F59">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F60">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F61">
@@ -3081,25 +3081,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">271115, 271116</t>
+          <t xml:space="preserve">7573379</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F62">
-        <v>6192</v>
+        <v>512</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311237694</t>
+          <t xml:space="preserve">311236497</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-30</t>
+          <t xml:space="preserve">2027-03-24</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3131,25 +3131,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">272010</t>
+          <t xml:space="preserve">7573379</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F63">
-        <v>1846</v>
+        <v>512</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311239403</t>
+          <t xml:space="preserve">311236497</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-06</t>
+          <t xml:space="preserve">2027-03-24</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3181,20 +3181,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">272010, 272011</t>
+          <t xml:space="preserve">5335169</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F64">
-        <v>1658</v>
+        <v>641</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311239402</t>
+          <t xml:space="preserve">311239463</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3231,25 +3231,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">5335169</t>
+          <t xml:space="preserve">8077237</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F65">
-        <v>641</v>
+        <v>470</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311239463</t>
+          <t xml:space="preserve">311242885</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-06</t>
+          <t xml:space="preserve">2027-04-25</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">8077237</t>
+          <t xml:space="preserve">5334475</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3290,16 +3290,16 @@
         </is>
       </c>
       <c r="F66">
-        <v>470</v>
+        <v>256</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311242885</t>
+          <t xml:space="preserve">311243209</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-25</t>
+          <t xml:space="preserve">2027-04-26</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">5334475</t>
+          <t xml:space="preserve">5334947</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3340,11 +3340,11 @@
         </is>
       </c>
       <c r="F67">
-        <v>256</v>
+        <v>410</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311243209</t>
+          <t xml:space="preserve">311243212</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">5334947</t>
+          <t xml:space="preserve">5334983</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3390,11 +3390,11 @@
         </is>
       </c>
       <c r="F68">
-        <v>410</v>
+        <v>8718</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311243212</t>
+          <t xml:space="preserve">311243219</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">5334983</t>
+          <t xml:space="preserve">7805439</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3440,11 +3440,11 @@
         </is>
       </c>
       <c r="F69">
-        <v>8718</v>
+        <v>540</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311243219</t>
+          <t xml:space="preserve">311243217</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3481,25 +3481,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">5339867</t>
+          <t xml:space="preserve">100044734</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F70">
-        <v>579</v>
+        <v>615</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311243160</t>
+          <t xml:space="preserve">311248907</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-26</t>
+          <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">7805439</t>
+          <t xml:space="preserve">2409849</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3540,16 +3540,16 @@
         </is>
       </c>
       <c r="F71">
-        <v>540</v>
+        <v>1876</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311243217</t>
+          <t xml:space="preserve">311248975</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-26</t>
+          <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">100044734</t>
+          <t xml:space="preserve">5339293</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3590,16 +3590,16 @@
         </is>
       </c>
       <c r="F72">
-        <v>615</v>
+        <v>1227</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248907</t>
+          <t xml:space="preserve">311249402</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-22</t>
+          <t xml:space="preserve">2027-05-23</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2409849</t>
+          <t xml:space="preserve">7637708</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3640,16 +3640,16 @@
         </is>
       </c>
       <c r="F73">
-        <v>1876</v>
+        <v>872</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248975</t>
+          <t xml:space="preserve">311250302</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-22</t>
+          <t xml:space="preserve">2027-05-29</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">5339293</t>
+          <t xml:space="preserve">2392048</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3690,16 +3690,16 @@
         </is>
       </c>
       <c r="F74">
-        <v>1227</v>
+        <v>1053</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311249402</t>
+          <t xml:space="preserve">311251071</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-23</t>
+          <t xml:space="preserve">2027-05-31</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">7637708</t>
+          <t xml:space="preserve">2401337</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3740,16 +3740,16 @@
         </is>
       </c>
       <c r="F75">
-        <v>872</v>
+        <v>1128</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311250302</t>
+          <t xml:space="preserve">311251192</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-29</t>
+          <t xml:space="preserve">2027-06-01</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3781,25 +3781,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2392048</t>
+          <t xml:space="preserve">2401337</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F76">
-        <v>1053</v>
+        <v>1731</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251071</t>
+          <t xml:space="preserve">311251192</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-31</t>
+          <t xml:space="preserve">2027-06-01</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3836,11 +3836,11 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F77">
-        <v>1128</v>
+        <v>2223</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3886,11 +3886,11 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F78">
-        <v>1731</v>
+        <v>795</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3931,25 +3931,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2401337</t>
+          <t xml:space="preserve">2384645</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F79">
-        <v>2223</v>
+        <v>439</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251192</t>
+          <t xml:space="preserve">311251898</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-01</t>
+          <t xml:space="preserve">2027-06-06</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3981,25 +3981,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2401337</t>
+          <t xml:space="preserve">2384645</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F80">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251192</t>
+          <t xml:space="preserve">311251899</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-01</t>
+          <t xml:space="preserve">2027-06-06</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2384645</t>
+          <t xml:space="preserve">2391781</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4040,16 +4040,16 @@
         </is>
       </c>
       <c r="F81">
-        <v>439</v>
+        <v>999</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251898</t>
+          <t xml:space="preserve">311258737</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-06</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4081,25 +4081,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2384645</t>
+          <t xml:space="preserve">2401302</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F82">
-        <v>799</v>
+        <v>564</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251899</t>
+          <t xml:space="preserve">311258791</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-06</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2391781</t>
+          <t xml:space="preserve">2408920</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4140,11 +4140,11 @@
         </is>
       </c>
       <c r="F83">
-        <v>999</v>
+        <v>754</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258737</t>
+          <t xml:space="preserve">311258825</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4181,20 +4181,20 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2401302</t>
+          <t xml:space="preserve">9415784</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="F84">
-        <v>564</v>
+        <v>1014</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258791</t>
+          <t xml:space="preserve">311258739</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408920</t>
+          <t xml:space="preserve">2408839</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4240,16 +4240,16 @@
         </is>
       </c>
       <c r="F85">
-        <v>754</v>
+        <v>840</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258825</t>
+          <t xml:space="preserve">311264148</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-08-02</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4281,25 +4281,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">9415784</t>
+          <t xml:space="preserve">719759, 2391621</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F86">
-        <v>1014</v>
+        <v>3125</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258739</t>
+          <t xml:space="preserve">311350102</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-09-05</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408839</t>
+          <t xml:space="preserve">2402709</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4340,16 +4340,16 @@
         </is>
       </c>
       <c r="F87">
-        <v>840</v>
+        <v>1724</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264148</t>
+          <t xml:space="preserve">311272027</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-02</t>
+          <t xml:space="preserve">2027-09-11</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4386,20 +4386,20 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F88">
-        <v>1724</v>
+        <v>346</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311272027</t>
+          <t xml:space="preserve">311272304</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-11</t>
+          <t xml:space="preserve">2027-09-12</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4431,25 +4431,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2402709</t>
+          <t xml:space="preserve">5334610</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F89">
-        <v>346</v>
+        <v>472</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311272304</t>
+          <t xml:space="preserve">311274663</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-12</t>
+          <t xml:space="preserve">2027-09-22</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">5334610</t>
+          <t xml:space="preserve">2408814</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4490,16 +4490,16 @@
         </is>
       </c>
       <c r="F90">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311274663</t>
+          <t xml:space="preserve">311276699</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-22</t>
+          <t xml:space="preserve">2027-10-04</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408814</t>
+          <t xml:space="preserve">719772, 2409825</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4540,11 +4540,11 @@
         </is>
       </c>
       <c r="F91">
-        <v>459</v>
+        <v>2306</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276699</t>
+          <t xml:space="preserve">311276692</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">267924, 267925, 267926</t>
+          <t xml:space="preserve">8282784</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -6040,16 +6040,16 @@
         </is>
       </c>
       <c r="F121">
-        <v>600</v>
+        <v>353</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352731</t>
+          <t xml:space="preserve">311403255</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-20</t>
+          <t xml:space="preserve">2029-10-10</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">270575</t>
+          <t xml:space="preserve">7380402</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6090,16 +6090,16 @@
         </is>
       </c>
       <c r="F122">
-        <v>2562</v>
+        <v>1944</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311354541</t>
+          <t xml:space="preserve">311448909</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-01-14</t>
+          <t xml:space="preserve">2030-07-09</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -6131,25 +6131,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">8282784</t>
+          <t xml:space="preserve">719742, 9386046</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F123">
-        <v>353</v>
+        <v>339</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311403255</t>
+          <t xml:space="preserve">311464714</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-10</t>
+          <t xml:space="preserve">2030-10-01</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">7380402</t>
+          <t xml:space="preserve">5339287</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -6190,16 +6190,16 @@
         </is>
       </c>
       <c r="F124">
-        <v>1944</v>
+        <v>840</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311448909</t>
+          <t xml:space="preserve">311658138</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-07-09</t>
+          <t xml:space="preserve">2033-02-06</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">5339287</t>
+          <t xml:space="preserve">2389399</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -6240,16 +6240,16 @@
         </is>
       </c>
       <c r="F125">
-        <v>840</v>
+        <v>1723</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311658138</t>
+          <t xml:space="preserve">311735788</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-06</t>
+          <t xml:space="preserve">2034-01-26</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2389399</t>
+          <t xml:space="preserve">10056287</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -6290,16 +6290,16 @@
         </is>
       </c>
       <c r="F126">
-        <v>1723</v>
+        <v>11883</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311735788</t>
+          <t xml:space="preserve">311834297</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-26</t>
+          <t xml:space="preserve">2035-05-26</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">10056287</t>
+          <t xml:space="preserve">2384021</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -6340,11 +6340,11 @@
         </is>
       </c>
       <c r="F127">
-        <v>11883</v>
+        <v>1872</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311834297</t>
+          <t xml:space="preserve">311834296</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -6386,15 +6386,15 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F128">
-        <v>1872</v>
+        <v>4238</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311834296</t>
+          <t xml:space="preserve">311834295</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -6431,25 +6431,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2384021</t>
+          <t xml:space="preserve">5338074</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F129">
-        <v>4238</v>
+        <v>1440</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311834295</t>
+          <t xml:space="preserve">311850583</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-26</t>
+          <t xml:space="preserve">2035-08-21</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6486,15 +6486,15 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F130">
-        <v>1440</v>
+        <v>301</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311850583</t>
+          <t xml:space="preserve">311850584</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -6536,15 +6536,15 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F131">
-        <v>301</v>
+        <v>1440</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311850586</t>
+          <t xml:space="preserve">311850583</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -6586,11 +6586,11 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F132">
-        <v>1440</v>
+        <v>1963</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -6636,11 +6636,11 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F133">
-        <v>1963</v>
+        <v>477</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -6686,11 +6686,11 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F134">
-        <v>477</v>
+        <v>1685</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -6736,15 +6736,15 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F135">
-        <v>1685</v>
+        <v>2108</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311850583</t>
+          <t xml:space="preserve">311850584</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -6786,15 +6786,15 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F136">
-        <v>2108</v>
+        <v>1440</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311850588</t>
+          <t xml:space="preserve">311850583</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -6831,25 +6831,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">5338074</t>
+          <t xml:space="preserve">7226325</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F137">
-        <v>1440</v>
+        <v>1188</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311850583</t>
+          <t xml:space="preserve">311851447</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-21</t>
+          <t xml:space="preserve">2035-08-26</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6886,15 +6886,15 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F138">
-        <v>1188</v>
+        <v>747</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851447</t>
+          <t xml:space="preserve">311851452</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -6936,15 +6936,15 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F139">
-        <v>747</v>
+        <v>431</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851452</t>
+          <t xml:space="preserve">311851447</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -6986,11 +6986,11 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F140">
-        <v>431</v>
+        <v>2038</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -7036,11 +7036,11 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F141">
-        <v>2038</v>
+        <v>735</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F142">
@@ -7136,11 +7136,11 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F143">
-        <v>735</v>
+        <v>1010</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -7186,11 +7186,11 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F144">
-        <v>1010</v>
+        <v>385</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -7236,11 +7236,11 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F145">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -7281,25 +7281,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">7226325</t>
+          <t xml:space="preserve">2410274</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F146">
-        <v>379</v>
+        <v>3739</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851447</t>
+          <t xml:space="preserve">311852051</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-26</t>
+          <t xml:space="preserve">2035-08-28</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -7331,20 +7331,20 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2410274</t>
+          <t xml:space="preserve">7564740</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F147">
-        <v>3739</v>
+        <v>261</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311852051</t>
+          <t xml:space="preserve">311852046</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -7386,15 +7386,15 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F148">
-        <v>261</v>
+        <v>640</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311852046</t>
+          <t xml:space="preserve">311852047</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -7431,25 +7431,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">7564740</t>
+          <t xml:space="preserve">7376334</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F149">
-        <v>640</v>
+        <v>1242</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311852047</t>
+          <t xml:space="preserve">311852541</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-28</t>
+          <t xml:space="preserve">2035-08-29</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">7376334</t>
+          <t xml:space="preserve">5339264</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -7490,16 +7490,16 @@
         </is>
       </c>
       <c r="F150">
-        <v>1242</v>
+        <v>2285</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311852541</t>
+          <t xml:space="preserve">311865119</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-29</t>
+          <t xml:space="preserve">2035-10-29</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">5339867</t>
+          <t xml:space="preserve">719717, 2384607</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -7540,16 +7540,16 @@
         </is>
       </c>
       <c r="F151">
-        <v>487</v>
+        <v>1096</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311852675</t>
+          <t xml:space="preserve">311865044</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-31</t>
+          <t xml:space="preserve">2035-10-29</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">5339867</t>
+          <t xml:space="preserve">8077972</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -7590,16 +7590,16 @@
         </is>
       </c>
       <c r="F152">
-        <v>348</v>
+        <v>280</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311852675</t>
+          <t xml:space="preserve">311865122</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-31</t>
+          <t xml:space="preserve">2035-10-29</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -7631,25 +7631,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">5339867</t>
+          <t xml:space="preserve">8285343</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F153">
-        <v>429</v>
+        <v>324</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311852675</t>
+          <t xml:space="preserve">311864983</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-31</t>
+          <t xml:space="preserve">2035-10-29</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -7681,25 +7681,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">5339867</t>
+          <t xml:space="preserve">8285343</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F154">
-        <v>396</v>
+        <v>2398</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311852675</t>
+          <t xml:space="preserve">311864985</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-31</t>
+          <t xml:space="preserve">2035-10-29</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -7731,25 +7731,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">5339867</t>
+          <t xml:space="preserve">8285343</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F155">
-        <v>439</v>
+        <v>1404</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311852675</t>
+          <t xml:space="preserve">311864985</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-31</t>
+          <t xml:space="preserve">2035-10-29</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -7781,25 +7781,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">5339867</t>
+          <t xml:space="preserve">5340835</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F156">
-        <v>396</v>
+        <v>283</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311852675</t>
+          <t xml:space="preserve">311865496</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-31</t>
+          <t xml:space="preserve">2035-10-30</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -7831,25 +7831,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">5339867</t>
+          <t xml:space="preserve">719735, 2395810</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F157">
-        <v>1293</v>
+        <v>1542</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311852676</t>
+          <t xml:space="preserve">311865658</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-31</t>
+          <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -7881,25 +7881,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">5339867</t>
+          <t xml:space="preserve">5335410</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F158">
-        <v>251</v>
+        <v>288</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311852676</t>
+          <t xml:space="preserve">311866223</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-31</t>
+          <t xml:space="preserve">2035-11-04</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -7931,25 +7931,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">5339264</t>
+          <t xml:space="preserve">5335410</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F159">
-        <v>2285</v>
+        <v>739</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865119</t>
+          <t xml:space="preserve">311866223</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-29</t>
+          <t xml:space="preserve">2035-11-04</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -7981,25 +7981,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">719717, 2384607</t>
+          <t xml:space="preserve">5335410</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F160">
-        <v>1096</v>
+        <v>640</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865044</t>
+          <t xml:space="preserve">311866223</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-29</t>
+          <t xml:space="preserve">2035-11-04</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -8031,25 +8031,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">7376333</t>
+          <t xml:space="preserve">2391265</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F161">
-        <v>2665</v>
+        <v>1511</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311864976</t>
+          <t xml:space="preserve">311866718</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-29</t>
+          <t xml:space="preserve">2035-11-06</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -8081,25 +8081,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">7376333</t>
+          <t xml:space="preserve">2391265</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F162">
-        <v>2066</v>
+        <v>1990</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311864976</t>
+          <t xml:space="preserve">311866718</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-29</t>
+          <t xml:space="preserve">2035-11-06</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">7376333</t>
+          <t xml:space="preserve">2391265</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -8140,16 +8140,16 @@
         </is>
       </c>
       <c r="F163">
-        <v>1115</v>
+        <v>796</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311864976</t>
+          <t xml:space="preserve">311866718</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-29</t>
+          <t xml:space="preserve">2035-11-06</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">7376333</t>
+          <t xml:space="preserve">2391265</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -8190,16 +8190,16 @@
         </is>
       </c>
       <c r="F164">
-        <v>466</v>
+        <v>836</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311864978</t>
+          <t xml:space="preserve">311866718</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-29</t>
+          <t xml:space="preserve">2035-11-06</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -8231,25 +8231,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">8077972</t>
+          <t xml:space="preserve">2402461</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F165">
-        <v>280</v>
+        <v>1804</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865122</t>
+          <t xml:space="preserve">311867558</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-29</t>
+          <t xml:space="preserve">2035-11-11</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -8281,25 +8281,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">8285343</t>
+          <t xml:space="preserve">2402461</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F166">
-        <v>324</v>
+        <v>280</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311864983</t>
+          <t xml:space="preserve">311867559</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-29</t>
+          <t xml:space="preserve">2035-11-11</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -8331,25 +8331,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">8285343</t>
+          <t xml:space="preserve">8820316</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F167">
-        <v>2398</v>
+        <v>729</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311864985</t>
+          <t xml:space="preserve">311867560</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-29</t>
+          <t xml:space="preserve">2035-11-11</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -8381,25 +8381,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">8285343</t>
+          <t xml:space="preserve">2395798</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F168">
-        <v>1404</v>
+        <v>467</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311864985</t>
+          <t xml:space="preserve">311867756</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-29</t>
+          <t xml:space="preserve">2035-11-12</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">5340835</t>
+          <t xml:space="preserve">2395790</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -8440,16 +8440,16 @@
         </is>
       </c>
       <c r="F169">
-        <v>283</v>
+        <v>452</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865496</t>
+          <t xml:space="preserve">311868836</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-30</t>
+          <t xml:space="preserve">2035-11-18</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -8481,25 +8481,25 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">719735, 2395810</t>
+          <t xml:space="preserve">2397479</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F170">
-        <v>1542</v>
+        <v>427</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865658</t>
+          <t xml:space="preserve">311872573</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-31</t>
+          <t xml:space="preserve">2035-12-09</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -8531,25 +8531,25 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">5335410</t>
+          <t xml:space="preserve">2397479</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F171">
-        <v>739</v>
+        <v>645</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866225</t>
+          <t xml:space="preserve">311872573</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-04</t>
+          <t xml:space="preserve">2035-12-09</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -8581,25 +8581,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">5335410</t>
+          <t xml:space="preserve">2397479</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F172">
-        <v>640</v>
+        <v>320</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866227</t>
+          <t xml:space="preserve">311872573</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-04</t>
+          <t xml:space="preserve">2035-12-09</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -8631,25 +8631,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2391265</t>
+          <t xml:space="preserve">2397479</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F173">
-        <v>1511</v>
+        <v>1402</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866718</t>
+          <t xml:space="preserve">311872573</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-06</t>
+          <t xml:space="preserve">2035-12-09</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -8681,25 +8681,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2391265</t>
+          <t xml:space="preserve">2397479</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F174">
-        <v>1990</v>
+        <v>290</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866718</t>
+          <t xml:space="preserve">311872576</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-06</t>
+          <t xml:space="preserve">2035-12-09</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -8731,25 +8731,25 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2391265</t>
+          <t xml:space="preserve">2400079, 100800056</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F175">
-        <v>796</v>
+        <v>1084</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866718</t>
+          <t xml:space="preserve">311874431</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-06</t>
+          <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -8781,25 +8781,25 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2391265</t>
+          <t xml:space="preserve">2400080, 100800076</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F176">
-        <v>836</v>
+        <v>1469</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866718</t>
+          <t xml:space="preserve">311874429</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-06</t>
+          <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2402461</t>
+          <t xml:space="preserve">5339867</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -8840,16 +8840,16 @@
         </is>
       </c>
       <c r="F177">
-        <v>1804</v>
+        <v>487</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311867558</t>
+          <t xml:space="preserve">311874453</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-11</t>
+          <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -8881,25 +8881,25 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2402461</t>
+          <t xml:space="preserve">5339867</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F178">
-        <v>280</v>
+        <v>579</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311867559</t>
+          <t xml:space="preserve">311874453</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-11</t>
+          <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -8931,25 +8931,25 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">8820316</t>
+          <t xml:space="preserve">5339867</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F179">
-        <v>729</v>
+        <v>348</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311867560</t>
+          <t xml:space="preserve">311874453</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-11</t>
+          <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -8981,25 +8981,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2395798</t>
+          <t xml:space="preserve">5339867</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F180">
-        <v>467</v>
+        <v>429</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311867756</t>
+          <t xml:space="preserve">311874453</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-12</t>
+          <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -9031,25 +9031,25 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2395790</t>
+          <t xml:space="preserve">5339867</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F181">
-        <v>452</v>
+        <v>396</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868836</t>
+          <t xml:space="preserve">311874453</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-18</t>
+          <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -9081,25 +9081,25 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2397479</t>
+          <t xml:space="preserve">5339867</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F182">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872573</t>
+          <t xml:space="preserve">311874453</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-09</t>
+          <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -9131,25 +9131,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2397479</t>
+          <t xml:space="preserve">5339867</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F183">
-        <v>645</v>
+        <v>396</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872573</t>
+          <t xml:space="preserve">311874453</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-09</t>
+          <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -9181,25 +9181,25 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2397479</t>
+          <t xml:space="preserve">5339867</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F184">
-        <v>320</v>
+        <v>1293</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872573</t>
+          <t xml:space="preserve">311874453</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-09</t>
+          <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -9231,25 +9231,25 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2397479</t>
+          <t xml:space="preserve">5339867</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F185">
-        <v>1402</v>
+        <v>251</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872573</t>
+          <t xml:space="preserve">311874453</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-09</t>
+          <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -9281,25 +9281,25 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2397479</t>
+          <t xml:space="preserve">7153439</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F186">
-        <v>290</v>
+        <v>960</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872576</t>
+          <t xml:space="preserve">311875725</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-09</t>
+          <t xml:space="preserve">2036-01-08</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -9331,25 +9331,25 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2400079, 100800056</t>
+          <t xml:space="preserve">100459791</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F187">
-        <v>1084</v>
+        <v>379</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874431</t>
+          <t xml:space="preserve">311880095</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-19</t>
+          <t xml:space="preserve">2036-02-03</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -9381,25 +9381,25 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2400080, 100800076</t>
+          <t xml:space="preserve">2402019</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F188">
-        <v>1469</v>
+        <v>348</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874429</t>
+          <t xml:space="preserve">311882274</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-19</t>
+          <t xml:space="preserve">2036-02-16</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">7153439</t>
+          <t xml:space="preserve">2402027</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -9440,16 +9440,16 @@
         </is>
       </c>
       <c r="F189">
-        <v>960</v>
+        <v>879</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875725</t>
+          <t xml:space="preserve">311882268</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-08</t>
+          <t xml:space="preserve">2036-02-16</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -9481,25 +9481,25 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">100459791</t>
+          <t xml:space="preserve">2402027</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F190">
-        <v>379</v>
+        <v>348</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311880095</t>
+          <t xml:space="preserve">311882269</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-03</t>
+          <t xml:space="preserve">2036-02-16</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -9531,20 +9531,20 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2402019</t>
+          <t xml:space="preserve">2402030</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F191">
-        <v>348</v>
+        <v>445</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311882274</t>
+          <t xml:space="preserve">311882265</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -9581,20 +9581,20 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2402027</t>
+          <t xml:space="preserve">2402030</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F192">
-        <v>879</v>
+        <v>592</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311882268</t>
+          <t xml:space="preserve">311882266</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -9631,25 +9631,25 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2402027</t>
+          <t xml:space="preserve">5340919</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F193">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311882275</t>
+          <t xml:space="preserve">311882720</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-16</t>
+          <t xml:space="preserve">2036-02-18</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -9681,25 +9681,25 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2402030</t>
+          <t xml:space="preserve">5340919</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F194">
-        <v>445</v>
+        <v>640</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311882265</t>
+          <t xml:space="preserve">311882720</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-16</t>
+          <t xml:space="preserve">2036-02-18</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -9731,25 +9731,25 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2402030</t>
+          <t xml:space="preserve">8921449</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F195">
-        <v>592</v>
+        <v>3302</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311882266</t>
+          <t xml:space="preserve">311888237</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-16</t>
+          <t xml:space="preserve">2036-03-18</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -9781,25 +9781,25 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">5340919</t>
+          <t xml:space="preserve">8921449</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F196">
-        <v>345</v>
+        <v>455</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311882720</t>
+          <t xml:space="preserve">311888240</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-18</t>
+          <t xml:space="preserve">2036-03-18</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -9831,25 +9831,25 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t xml:space="preserve">5340919</t>
+          <t xml:space="preserve">9167622</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F197">
-        <v>640</v>
+        <v>1082</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311882720</t>
+          <t xml:space="preserve">311893637</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-18</t>
+          <t xml:space="preserve">2036-04-13</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -9881,25 +9881,25 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t xml:space="preserve">8921449</t>
+          <t xml:space="preserve">719732, 5336412</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F198">
-        <v>3302</v>
+        <v>632</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888237</t>
+          <t xml:space="preserve">311898603</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-18</t>
+          <t xml:space="preserve">2036-05-04</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -9931,25 +9931,25 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t xml:space="preserve">8921449</t>
+          <t xml:space="preserve">2391620</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F199">
-        <v>455</v>
+        <v>722</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888240</t>
+          <t xml:space="preserve">311903997</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-18</t>
+          <t xml:space="preserve">2036-05-27</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -9981,25 +9981,25 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t xml:space="preserve">9167622</t>
+          <t xml:space="preserve">2391620</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F200">
-        <v>1082</v>
+        <v>640</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311893637</t>
+          <t xml:space="preserve">311903995</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-13</t>
+          <t xml:space="preserve">2036-05-27</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -10031,25 +10031,25 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t xml:space="preserve">719732, 5336412</t>
+          <t xml:space="preserve">2391620</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F201">
-        <v>632</v>
+        <v>441</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311898603</t>
+          <t xml:space="preserve">311903995</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-04</t>
+          <t xml:space="preserve">2036-05-27</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -10086,15 +10086,15 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F202">
-        <v>722</v>
+        <v>654</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903997</t>
+          <t xml:space="preserve">311903995</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -10136,11 +10136,11 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F203">
-        <v>640</v>
+        <v>4699</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
@@ -10186,11 +10186,11 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F204">
-        <v>441</v>
+        <v>622</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
@@ -10231,20 +10231,20 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2391620</t>
+          <t xml:space="preserve">2408102</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F205">
-        <v>654</v>
+        <v>1080</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903995</t>
+          <t xml:space="preserve">311904052</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -10281,20 +10281,20 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2391620</t>
+          <t xml:space="preserve">5340689</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F206">
-        <v>4699</v>
+        <v>634</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903995</t>
+          <t xml:space="preserve">311904029</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -10331,20 +10331,20 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2391620</t>
+          <t xml:space="preserve">719778, 2408102</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F207">
-        <v>622</v>
+        <v>2048</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903995</t>
+          <t xml:space="preserve">311904037</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408102</t>
+          <t xml:space="preserve">7618119</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -10390,16 +10390,16 @@
         </is>
       </c>
       <c r="F208">
-        <v>1080</v>
+        <v>4058</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311904052</t>
+          <t xml:space="preserve">311905846</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-27</t>
+          <t xml:space="preserve">2036-06-04</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -10431,25 +10431,25 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">265333, 265334</t>
+          <t xml:space="preserve">7618119</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F209">
-        <v>418</v>
+        <v>382</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311904008</t>
+          <t xml:space="preserve">311905846</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-27</t>
+          <t xml:space="preserve">2036-06-04</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t xml:space="preserve">5340689</t>
+          <t xml:space="preserve">2408076</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -10490,16 +10490,16 @@
         </is>
       </c>
       <c r="F210">
-        <v>634</v>
+        <v>2062</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311904029</t>
+          <t xml:space="preserve">311909485</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-27</t>
+          <t xml:space="preserve">2036-06-19</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -10531,25 +10531,25 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t xml:space="preserve">719778, 2408102</t>
+          <t xml:space="preserve">2408076</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F211">
-        <v>2048</v>
+        <v>376</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311904037</t>
+          <t xml:space="preserve">311909486</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-27</t>
+          <t xml:space="preserve">2036-06-19</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t xml:space="preserve">7618119</t>
+          <t xml:space="preserve">7960027</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -10590,16 +10590,16 @@
         </is>
       </c>
       <c r="F212">
-        <v>4058</v>
+        <v>519</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905846</t>
+          <t xml:space="preserve">311910894</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-04</t>
+          <t xml:space="preserve">2036-06-25</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -10631,25 +10631,25 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t xml:space="preserve">7618119</t>
+          <t xml:space="preserve">10218277</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F213">
-        <v>382</v>
+        <v>1088</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905846</t>
+          <t xml:space="preserve">311911479</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-04</t>
+          <t xml:space="preserve">2036-06-29</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -10681,25 +10681,25 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408076</t>
+          <t xml:space="preserve">7095821</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F214">
-        <v>2062</v>
+        <v>802</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311909485</t>
+          <t xml:space="preserve">311911466</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-19</t>
+          <t xml:space="preserve">2036-06-29</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -10731,25 +10731,25 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408076</t>
+          <t xml:space="preserve">7095821</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F215">
-        <v>376</v>
+        <v>1348</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311909486</t>
+          <t xml:space="preserve">311911466</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-19</t>
+          <t xml:space="preserve">2036-06-29</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -10781,7 +10781,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t xml:space="preserve">7960027</t>
+          <t xml:space="preserve">2399272</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -10790,16 +10790,16 @@
         </is>
       </c>
       <c r="F216">
-        <v>519</v>
+        <v>5665</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311910894</t>
+          <t xml:space="preserve">311911823</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-25</t>
+          <t xml:space="preserve">2036-06-30</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -10831,25 +10831,25 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t xml:space="preserve">10218277</t>
+          <t xml:space="preserve">2399272</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F217">
-        <v>1088</v>
+        <v>1315</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911479</t>
+          <t xml:space="preserve">311911823</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-29</t>
+          <t xml:space="preserve">2036-06-30</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -10881,25 +10881,25 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t xml:space="preserve">7095821</t>
+          <t xml:space="preserve">2399272</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F218">
-        <v>802</v>
+        <v>1277</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911471</t>
+          <t xml:space="preserve">311911823</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-29</t>
+          <t xml:space="preserve">2036-06-30</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -10931,25 +10931,25 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t xml:space="preserve">7095821</t>
+          <t xml:space="preserve">2393534</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F219">
-        <v>1348</v>
+        <v>2664</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911474</t>
+          <t xml:space="preserve">311912618</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-29</t>
+          <t xml:space="preserve">2036-07-03</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -10981,25 +10981,25 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t xml:space="preserve">7376333</t>
+          <t xml:space="preserve">2393534</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F220">
-        <v>352</v>
+        <v>673</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911482</t>
+          <t xml:space="preserve">311912618</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-29</t>
+          <t xml:space="preserve">2036-07-03</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -11031,25 +11031,25 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2399272</t>
+          <t xml:space="preserve">7376333</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F221">
-        <v>5665</v>
+        <v>2665</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911830</t>
+          <t xml:space="preserve">311912624</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-30</t>
+          <t xml:space="preserve">2036-07-03</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -11081,25 +11081,25 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2399272</t>
+          <t xml:space="preserve">7376333</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F222">
-        <v>1315</v>
+        <v>2066</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911826</t>
+          <t xml:space="preserve">311912624</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-30</t>
+          <t xml:space="preserve">2036-07-03</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -11131,7 +11131,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2399272</t>
+          <t xml:space="preserve">7376333</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -11140,16 +11140,16 @@
         </is>
       </c>
       <c r="F223">
-        <v>1277</v>
+        <v>1115</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911826</t>
+          <t xml:space="preserve">311912624</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-30</t>
+          <t xml:space="preserve">2036-07-03</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -11181,20 +11181,20 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2393534</t>
+          <t xml:space="preserve">7376333</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F224">
-        <v>2664</v>
+        <v>352</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311912618</t>
+          <t xml:space="preserve">311912624</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -11231,20 +11231,20 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t xml:space="preserve">2393534</t>
+          <t xml:space="preserve">7376333</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F225">
-        <v>673</v>
+        <v>466</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311912618</t>
+          <t xml:space="preserve">311912624</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">

--- a/public/exports/29189447.xlsx
+++ b/public/exports/29189447.xlsx
@@ -151,26 +151,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Forten 10</t>
+          <t xml:space="preserve">Asmindrupvej 50</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4390</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100367073</t>
+          <t xml:space="preserve">2399271</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H3">
-        <v>1373</v>
+        <v>669</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,26 +211,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyvangs Allé 4</t>
+          <t xml:space="preserve">Asmindrupvej 50</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4390</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">100367074</t>
+          <t xml:space="preserve">2399271</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H4">
-        <v>798</v>
+        <v>669</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,26 +271,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østervænget 1</t>
+          <t xml:space="preserve">Asmindrupvej 50</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4390</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">100367074</t>
+          <t xml:space="preserve">2399271</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H5">
-        <v>2032</v>
+        <v>589</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,7 +331,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Traktørstien 3</t>
+          <t xml:space="preserve">Borgmester B. Kristiansens Vej 8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -346,11 +346,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="H6">
-        <v>415</v>
+        <v>293</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,7 +391,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgmester B. Kristiansens Vej 8</t>
+          <t xml:space="preserve">Borgmestergårdsvej 3A</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -401,16 +401,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">100367074</t>
+          <t xml:space="preserve">719728, 5340331</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H7">
-        <v>293</v>
+        <v>268</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,26 +451,26 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Forten 2</t>
+          <t xml:space="preserve">Brændholtvej 5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4350</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">100367074</t>
+          <t xml:space="preserve">2410400</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H8">
-        <v>338</v>
+        <v>713</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -511,26 +511,26 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mejerivangen 4</t>
+          <t xml:space="preserve">Bygaden 50</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4305</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">100367074</t>
+          <t xml:space="preserve">2395800</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H9">
-        <v>360</v>
+        <v>419</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyvangs Allé 1</t>
+          <t xml:space="preserve">Carl Reffsvej 20</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -581,16 +581,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">100367074</t>
+          <t xml:space="preserve">5335507</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H10">
-        <v>451</v>
+        <v>412</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -631,26 +631,26 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanevej 4</t>
+          <t xml:space="preserve">Dragerupvej 50</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2387376</t>
+          <t xml:space="preserve">719610, 2398678</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H11">
-        <v>257</v>
+        <v>591</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 50</t>
+          <t xml:space="preserve">Dragerupvej 50</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">4305</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2395800</t>
+          <t xml:space="preserve">719610, 2398678</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H12">
-        <v>419</v>
+        <v>398</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -751,26 +751,26 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asmindrupvej 50</t>
+          <t xml:space="preserve">Forten 10</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">4390</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2399271</t>
+          <t xml:space="preserve">100367073</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H13">
-        <v>669</v>
+        <v>1373</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -811,26 +811,26 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asmindrupvej 50</t>
+          <t xml:space="preserve">Forten 2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">4390</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2399271</t>
+          <t xml:space="preserve">100367074</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H14">
-        <v>669</v>
+        <v>338</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -871,26 +871,26 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asmindrupvej 50</t>
+          <t xml:space="preserve">Jernbanevej 4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">4390</t>
+          <t xml:space="preserve">4450</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2399271</t>
+          <t xml:space="preserve">2387376</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H15">
-        <v>589</v>
+        <v>257</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -931,26 +931,26 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændholtvej 5</t>
+          <t xml:space="preserve">Jernbanevej 6</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">4350</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2410400</t>
+          <t xml:space="preserve">5334983</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H16">
-        <v>713</v>
+        <v>354</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hybenvang 61A</t>
+          <t xml:space="preserve">Kanalstræde 21</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">265333, 265334</t>
+          <t xml:space="preserve">5334804</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="H17">
-        <v>418</v>
+        <v>1813</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuse Byvej 24</t>
+          <t xml:space="preserve">Kapellanvej 4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">265751, 265752</t>
+          <t xml:space="preserve">719739, 5336599</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="H18">
-        <v>939</v>
+        <v>325</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanevej 29A</t>
+          <t xml:space="preserve">Mejerivangen 4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1121,16 +1121,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">267924, 267925, 267926</t>
+          <t xml:space="preserve">100367074</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c r="H19">
-        <v>600</v>
+        <v>360</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1171,17 +1171,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carl Reffsvej 2</t>
+          <t xml:space="preserve">Nordgårde 4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4520</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">270089</t>
+          <t xml:space="preserve">719761, 2391872</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="H20">
-        <v>2052</v>
+        <v>328</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1231,26 +1231,26 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søbæksvej 30</t>
+          <t xml:space="preserve">Nyvangs Allé 1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">270575</t>
+          <t xml:space="preserve">100367074</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="H21">
-        <v>2562</v>
+        <v>451</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenhusvej 21</t>
+          <t xml:space="preserve">Nyvangs Allé 4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">271115, 271116</t>
+          <t xml:space="preserve">100367074</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="H22">
-        <v>6192</v>
+        <v>798</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Tuse Næs Vej 15B</t>
+          <t xml:space="preserve">Traktørstien 3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1361,16 +1361,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">272010</t>
+          <t xml:space="preserve">100367074</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H23">
-        <v>1846</v>
+        <v>415</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Tuse Næs Vej 15A</t>
+          <t xml:space="preserve">Vimmelskaftet 27</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">272010, 272011</t>
+          <t xml:space="preserve">5334883</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1430,7 +1430,7 @@
         </is>
       </c>
       <c r="H24">
-        <v>1658</v>
+        <v>1071</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kanalstræde 21</t>
+          <t xml:space="preserve">Østervænget 1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1481,16 +1481,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5334804</t>
+          <t xml:space="preserve">100367074</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H25">
-        <v>1813</v>
+        <v>2032</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vimmelskaftet 27</t>
+          <t xml:space="preserve">Højen 38</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1541,30 +1541,30 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5334883</t>
+          <t xml:space="preserve">5336438</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H26">
-        <v>1071</v>
+        <v>2726</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200020593</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-09-17</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1591,40 +1591,40 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanevej 6</t>
+          <t xml:space="preserve">Holbækvej 30C</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4370</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5334983</t>
+          <t xml:space="preserve">2408102</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H27">
-        <v>354</v>
+        <v>489</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200031720</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-05-25</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -1651,40 +1651,40 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carl Reffsvej 20</t>
+          <t xml:space="preserve">Holbækvej 108A</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4450</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5335507</t>
+          <t xml:space="preserve">7226325</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H28">
-        <v>412</v>
+        <v>439</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200042618</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-12-08</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dragerupvej 50</t>
+          <t xml:space="preserve">Kalundborgvej 54F</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1721,30 +1721,30 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">719610, 2398678</t>
+          <t xml:space="preserve">719616, 5339534</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H29">
-        <v>591</v>
+        <v>671</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200047054</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-03-21</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dragerupvej 50</t>
+          <t xml:space="preserve">Chr Hansensvej 11A</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1781,35 +1781,35 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">719610, 2398678</t>
+          <t xml:space="preserve">5335077</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H30">
-        <v>398</v>
+        <v>310</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311218750</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-12-20</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1831,45 +1831,45 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgmestergårdsvej 3A</t>
+          <t xml:space="preserve">Centervænget 2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4390</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">719728, 5340331</t>
+          <t xml:space="preserve">2399431</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H31">
-        <v>268</v>
+        <v>326</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311219459</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1891,45 +1891,45 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kapellanvej 4</t>
+          <t xml:space="preserve">Centervænget 4</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4390</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">719739, 5336599</t>
+          <t xml:space="preserve">2399431</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H32">
-        <v>325</v>
+        <v>400</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311219459</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1951,17 +1951,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordgårde 4</t>
+          <t xml:space="preserve">Tuse Byvej 26</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">4520</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">719761, 2391872</t>
+          <t xml:space="preserve">2393544</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1970,26 +1970,26 @@
         </is>
       </c>
       <c r="H33">
-        <v>328</v>
+        <v>464</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311219966</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-12-29</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højen 38</t>
+          <t xml:space="preserve">Tuse Byvej 42</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">5336438</t>
+          <t xml:space="preserve">2393544</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2030,26 +2030,26 @@
         </is>
       </c>
       <c r="H34">
-        <v>2726</v>
+        <v>464</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020593</t>
+          <t xml:space="preserve">311219966</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-17</t>
+          <t xml:space="preserve">2026-12-29</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2071,45 +2071,45 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holbækvej 30C</t>
+          <t xml:space="preserve">Tuse Byvej 58</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">4370</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408102</t>
+          <t xml:space="preserve">2393544</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H35">
-        <v>489</v>
+        <v>464</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">200031720</t>
+          <t xml:space="preserve">311219966</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-05-25</t>
+          <t xml:space="preserve">2026-12-29</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2131,45 +2131,45 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holbækvej 108A</t>
+          <t xml:space="preserve">Tuse Byvej 74</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">7226325</t>
+          <t xml:space="preserve">2393544</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H36">
-        <v>439</v>
+        <v>464</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">200042636</t>
+          <t xml:space="preserve">311219966</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-08</t>
+          <t xml:space="preserve">2026-12-29</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalundborgvej 54F</t>
+          <t xml:space="preserve">Bispehøjen 4</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2201,35 +2201,35 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">719616, 5339534</t>
+          <t xml:space="preserve">5336543</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H37">
-        <v>671</v>
+        <v>606</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">200047054</t>
+          <t xml:space="preserve">311220222</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-03-21</t>
+          <t xml:space="preserve">2027-01-02</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chr Hansensvej 11A</t>
+          <t xml:space="preserve">Gasværksvej 9</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5335077</t>
+          <t xml:space="preserve">5334816</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2270,16 +2270,16 @@
         </is>
       </c>
       <c r="H38">
-        <v>310</v>
+        <v>1192</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311218750</t>
+          <t xml:space="preserve">311220229</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-20</t>
+          <t xml:space="preserve">2027-01-02</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2311,35 +2311,35 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Centervænget 4</t>
+          <t xml:space="preserve">Konsul Beÿers Allé 1A</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">4390</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2399431</t>
+          <t xml:space="preserve">8366959</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H39">
-        <v>400</v>
+        <v>509</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219459</t>
+          <t xml:space="preserve">311220673</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-22</t>
+          <t xml:space="preserve">2027-01-04</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2371,35 +2371,35 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Centervænget 2</t>
+          <t xml:space="preserve">Tuse Byvej 24</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">4390</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2399431</t>
+          <t xml:space="preserve">265751, 265752</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H40">
-        <v>326</v>
+        <v>939</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219459</t>
+          <t xml:space="preserve">311222478</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-22</t>
+          <t xml:space="preserve">2027-01-13</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2431,17 +2431,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuse Byvej 26</t>
+          <t xml:space="preserve">Sønderstrupvej 26</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2393544</t>
+          <t xml:space="preserve">100078242</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2450,16 +2450,16 @@
         </is>
       </c>
       <c r="H41">
-        <v>464</v>
+        <v>6249</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219966</t>
+          <t xml:space="preserve">311225362</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-29</t>
+          <t xml:space="preserve">2027-01-30</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuse Byvej 42</t>
+          <t xml:space="preserve">Kasernevej 6</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2501,25 +2501,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2393544</t>
+          <t xml:space="preserve">8033723</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H42">
-        <v>464</v>
+        <v>2314</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219966</t>
+          <t xml:space="preserve">311229616</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-29</t>
+          <t xml:space="preserve">2027-02-21</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuse Byvej 58</t>
+          <t xml:space="preserve">Rørvangsvej 4</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2561,25 +2561,25 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2393544</t>
+          <t xml:space="preserve">5340673</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H43">
-        <v>464</v>
+        <v>1017</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219966</t>
+          <t xml:space="preserve">311233036</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-29</t>
+          <t xml:space="preserve">2027-03-09</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuse Byvej 74</t>
+          <t xml:space="preserve">Karensmindevej 7</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2621,25 +2621,25 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2393544</t>
+          <t xml:space="preserve">5335611</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H44">
-        <v>464</v>
+        <v>1170</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219966</t>
+          <t xml:space="preserve">311233787</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-29</t>
+          <t xml:space="preserve">2027-03-13</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasværksvej 9</t>
+          <t xml:space="preserve">Munkevænget 38</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">5334816</t>
+          <t xml:space="preserve">5336544</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2690,16 +2690,16 @@
         </is>
       </c>
       <c r="H45">
-        <v>1192</v>
+        <v>730</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311220229</t>
+          <t xml:space="preserve">311233788</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-02</t>
+          <t xml:space="preserve">2027-03-13</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bispehøjen 4</t>
+          <t xml:space="preserve">Carl Reffsvej 2</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">5336543</t>
+          <t xml:space="preserve">270089</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2750,16 +2750,16 @@
         </is>
       </c>
       <c r="H46">
-        <v>606</v>
+        <v>2052</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311220222</t>
+          <t xml:space="preserve">311234340</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-02</t>
+          <t xml:space="preserve">2027-03-15</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Konsul Beÿers Allé 1A</t>
+          <t xml:space="preserve">Carl Reffsvej 32</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2801,25 +2801,25 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">8366959</t>
+          <t xml:space="preserve">5335507</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H47">
-        <v>509</v>
+        <v>306</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311220673</t>
+          <t xml:space="preserve">311234425</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-04</t>
+          <t xml:space="preserve">2027-03-15</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -2851,35 +2851,35 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderstrupvej 26</t>
+          <t xml:space="preserve">Carl Reffsvej 42</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">100078242</t>
+          <t xml:space="preserve">5335507</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H48">
-        <v>6249</v>
+        <v>1244</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225362</t>
+          <t xml:space="preserve">311234435</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-30</t>
+          <t xml:space="preserve">2027-03-15</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kasernevej 6</t>
+          <t xml:space="preserve">Carl Reffsvej 78</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2921,25 +2921,25 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">8033723</t>
+          <t xml:space="preserve">5335507</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H49">
-        <v>2314</v>
+        <v>306</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311229616</t>
+          <t xml:space="preserve">311234425</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-21</t>
+          <t xml:space="preserve">2027-03-15</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rørvangsvej 4</t>
+          <t xml:space="preserve">Carl Reffsvej 8</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2981,25 +2981,25 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">5340673</t>
+          <t xml:space="preserve">5335507</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H50">
-        <v>1017</v>
+        <v>412</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311233036</t>
+          <t xml:space="preserve">311234425</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-09</t>
+          <t xml:space="preserve">2027-03-15</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karensmindevej 7</t>
+          <t xml:space="preserve">Carl Reffsvej 88</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">5335611</t>
+          <t xml:space="preserve">5335507</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3050,16 +3050,16 @@
         </is>
       </c>
       <c r="H51">
-        <v>1170</v>
+        <v>303</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311233787</t>
+          <t xml:space="preserve">311234423</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-13</t>
+          <t xml:space="preserve">2027-03-15</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Munkevænget 38</t>
+          <t xml:space="preserve">Mellemvang 9</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">5336544</t>
+          <t xml:space="preserve">5340827</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3110,16 +3110,16 @@
         </is>
       </c>
       <c r="H52">
-        <v>730</v>
+        <v>1983</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311233788</t>
+          <t xml:space="preserve">311234426</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-13</t>
+          <t xml:space="preserve">2027-03-15</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carl Reffsvej 88</t>
+          <t xml:space="preserve">Stenhusvej 23A</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">5335507</t>
+          <t xml:space="preserve">7573379</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3170,16 +3170,16 @@
         </is>
       </c>
       <c r="H53">
-        <v>303</v>
+        <v>512</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234423</t>
+          <t xml:space="preserve">311236497</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-15</t>
+          <t xml:space="preserve">2027-03-24</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carl Reffsvej 8</t>
+          <t xml:space="preserve">Stenhusvej 25A</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">5335507</t>
+          <t xml:space="preserve">7573379</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3230,16 +3230,16 @@
         </is>
       </c>
       <c r="H54">
-        <v>412</v>
+        <v>512</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234425</t>
+          <t xml:space="preserve">311236497</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-15</t>
+          <t xml:space="preserve">2027-03-24</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carl Reffsvej 32</t>
+          <t xml:space="preserve">Stenhusvej 27A</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5335507</t>
+          <t xml:space="preserve">7573379</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3290,16 +3290,16 @@
         </is>
       </c>
       <c r="H55">
-        <v>306</v>
+        <v>512</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234425</t>
+          <t xml:space="preserve">311236497</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-15</t>
+          <t xml:space="preserve">2027-03-24</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carl Reffsvej 42</t>
+          <t xml:space="preserve">Stenhusvej 29A</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">5335507</t>
+          <t xml:space="preserve">7573379</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3350,16 +3350,16 @@
         </is>
       </c>
       <c r="H56">
-        <v>1244</v>
+        <v>512</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234435</t>
+          <t xml:space="preserve">311236497</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-15</t>
+          <t xml:space="preserve">2027-03-24</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carl Reffsvej 78</t>
+          <t xml:space="preserve">Stenhusvej 31A</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">5335507</t>
+          <t xml:space="preserve">7573379</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3410,16 +3410,16 @@
         </is>
       </c>
       <c r="H57">
-        <v>306</v>
+        <v>512</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234425</t>
+          <t xml:space="preserve">311236497</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-15</t>
+          <t xml:space="preserve">2027-03-24</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mellemvang 9</t>
+          <t xml:space="preserve">Stenhusvej 21</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">5340827</t>
+          <t xml:space="preserve">271115, 271116</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3470,16 +3470,16 @@
         </is>
       </c>
       <c r="H58">
-        <v>1983</v>
+        <v>6192</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234426</t>
+          <t xml:space="preserve">311237694</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-15</t>
+          <t xml:space="preserve">2027-03-30</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenhusvej 23A</t>
+          <t xml:space="preserve">Gl Tuse Næs Vej 15A</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">7573379</t>
+          <t xml:space="preserve">272010, 272011</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3530,16 +3530,16 @@
         </is>
       </c>
       <c r="H59">
-        <v>512</v>
+        <v>1658</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311236497</t>
+          <t xml:space="preserve">311239402</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-24</t>
+          <t xml:space="preserve">2027-04-06</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenhusvej 25A</t>
+          <t xml:space="preserve">Gl Tuse Næs Vej 15B</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3581,25 +3581,25 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">7573379</t>
+          <t xml:space="preserve">272010</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H60">
-        <v>512</v>
+        <v>1846</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311236497</t>
+          <t xml:space="preserve">311239403</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-24</t>
+          <t xml:space="preserve">2027-04-06</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenhusvej 27A</t>
+          <t xml:space="preserve">Tidemandsvej 1A</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3641,25 +3641,25 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">7573379</t>
+          <t xml:space="preserve">5335169</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H61">
-        <v>512</v>
+        <v>641</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311236497</t>
+          <t xml:space="preserve">311239463</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-24</t>
+          <t xml:space="preserve">2027-04-06</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenhusvej 29A</t>
+          <t xml:space="preserve">Kattegatsvej 11</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3701,25 +3701,25 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">7573379</t>
+          <t xml:space="preserve">8077237</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H62">
-        <v>512</v>
+        <v>470</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311236497</t>
+          <t xml:space="preserve">311242885</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-24</t>
+          <t xml:space="preserve">2027-04-25</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenhusvej 31A</t>
+          <t xml:space="preserve">Jernbanevej 6</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3761,25 +3761,25 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">7573379</t>
+          <t xml:space="preserve">5334983</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H63">
-        <v>512</v>
+        <v>8718</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311236497</t>
+          <t xml:space="preserve">311243219</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-24</t>
+          <t xml:space="preserve">2027-04-26</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tidemandsvej 1A</t>
+          <t xml:space="preserve">Rolighedsstræde 2</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3821,25 +3821,25 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5335169</t>
+          <t xml:space="preserve">5334475</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H64">
-        <v>641</v>
+        <v>256</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311239463</t>
+          <t xml:space="preserve">311243209</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-06</t>
+          <t xml:space="preserve">2027-04-26</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kattegatsvej 11</t>
+          <t xml:space="preserve">Rolighedsstræde 5</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">8077237</t>
+          <t xml:space="preserve">5334947</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3890,16 +3890,16 @@
         </is>
       </c>
       <c r="H65">
-        <v>470</v>
+        <v>410</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311242885</t>
+          <t xml:space="preserve">311243212</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-25</t>
+          <t xml:space="preserve">2027-04-26</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolighedsstræde 2</t>
+          <t xml:space="preserve">Roskildevej 12</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">5334475</t>
+          <t xml:space="preserve">7805439</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3950,11 +3950,11 @@
         </is>
       </c>
       <c r="H66">
-        <v>256</v>
+        <v>540</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311243209</t>
+          <t xml:space="preserve">311243217</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3991,17 +3991,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolighedsstræde 5</t>
+          <t xml:space="preserve">Ellebjergvej 31B</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4450</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">5334947</t>
+          <t xml:space="preserve">100044734</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4010,16 +4010,16 @@
         </is>
       </c>
       <c r="H67">
-        <v>410</v>
+        <v>615</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311243212</t>
+          <t xml:space="preserve">311248907</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-26</t>
+          <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4051,17 +4051,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanevej 6</t>
+          <t xml:space="preserve">Hjortholmvej 9A</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">5334983</t>
+          <t xml:space="preserve">2409849</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4070,16 +4070,16 @@
         </is>
       </c>
       <c r="H68">
-        <v>8718</v>
+        <v>1876</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311243219</t>
+          <t xml:space="preserve">311248975</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-26</t>
+          <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roskildevej 12</t>
+          <t xml:space="preserve">Kikhøjparken 1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">7805439</t>
+          <t xml:space="preserve">5339293</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4130,16 +4130,16 @@
         </is>
       </c>
       <c r="H69">
-        <v>540</v>
+        <v>1227</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311243217</t>
+          <t xml:space="preserve">311249402</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-26</t>
+          <t xml:space="preserve">2027-05-23</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4171,17 +4171,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ellebjergvej 31B</t>
+          <t xml:space="preserve">Blomstervænget 2</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450</t>
+          <t xml:space="preserve">4420</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">100044734</t>
+          <t xml:space="preserve">7637708</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4190,16 +4190,16 @@
         </is>
       </c>
       <c r="H70">
-        <v>615</v>
+        <v>872</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248907</t>
+          <t xml:space="preserve">311250302</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-22</t>
+          <t xml:space="preserve">2027-05-29</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4231,17 +4231,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjortholmvej 9A</t>
+          <t xml:space="preserve">Byparken 2</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4520</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2409849</t>
+          <t xml:space="preserve">2392048</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4250,16 +4250,16 @@
         </is>
       </c>
       <c r="H71">
-        <v>1876</v>
+        <v>1053</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248975</t>
+          <t xml:space="preserve">311251071</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-22</t>
+          <t xml:space="preserve">2027-05-31</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kikhøjparken 1</t>
+          <t xml:space="preserve">Gl. Skovvej 150C</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4420</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">5339293</t>
+          <t xml:space="preserve">2401337</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4310,16 +4310,16 @@
         </is>
       </c>
       <c r="H72">
-        <v>1227</v>
+        <v>1128</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311249402</t>
+          <t xml:space="preserve">311251192</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-23</t>
+          <t xml:space="preserve">2027-06-01</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blomstervænget 2</t>
+          <t xml:space="preserve">Gl. Skovvej 150C</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4361,25 +4361,25 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">7637708</t>
+          <t xml:space="preserve">2401337</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H73">
-        <v>872</v>
+        <v>1731</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311250302</t>
+          <t xml:space="preserve">311251192</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-29</t>
+          <t xml:space="preserve">2027-06-01</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4411,35 +4411,35 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byparken 2</t>
+          <t xml:space="preserve">Gl. Skovvej 150C</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">4520</t>
+          <t xml:space="preserve">4420</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2392048</t>
+          <t xml:space="preserve">2401337</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H74">
-        <v>1053</v>
+        <v>2223</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251071</t>
+          <t xml:space="preserve">311251192</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-31</t>
+          <t xml:space="preserve">2027-06-01</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4486,11 +4486,11 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H75">
-        <v>1128</v>
+        <v>795</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -4531,17 +4531,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Skovvej 150C</t>
+          <t xml:space="preserve">Damvej 14A</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">4420</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2401337</t>
+          <t xml:space="preserve">2384645</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4550,16 +4550,16 @@
         </is>
       </c>
       <c r="H76">
-        <v>1731</v>
+        <v>799</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251192</t>
+          <t xml:space="preserve">311251899</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-01</t>
+          <t xml:space="preserve">2027-06-06</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4591,35 +4591,35 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Skovvej 150C</t>
+          <t xml:space="preserve">Damvej 14B</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">4420</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2401337</t>
+          <t xml:space="preserve">2384645</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H77">
-        <v>2223</v>
+        <v>439</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251192</t>
+          <t xml:space="preserve">311251898</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-01</t>
+          <t xml:space="preserve">2027-06-06</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Skovvej 150C</t>
+          <t xml:space="preserve">Holløsevej 10C</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4661,25 +4661,25 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2401337</t>
+          <t xml:space="preserve">2401302</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H78">
-        <v>795</v>
+        <v>564</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251192</t>
+          <t xml:space="preserve">311258791</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-01</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4711,35 +4711,35 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Damvej 14B</t>
+          <t xml:space="preserve">Hovedgaden 40</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2384645</t>
+          <t xml:space="preserve">9415784</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="H79">
-        <v>439</v>
+        <v>1014</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251898</t>
+          <t xml:space="preserve">311258739</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-06</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -4771,35 +4771,35 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Damvej 14A</t>
+          <t xml:space="preserve">Hovedgaden 59</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4520</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2384645</t>
+          <t xml:space="preserve">2391781</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H80">
-        <v>799</v>
+        <v>999</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251899</t>
+          <t xml:space="preserve">311258737</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-06</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4831,17 +4831,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 59</t>
+          <t xml:space="preserve">Jernbanevej 18E</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">4520</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2391781</t>
+          <t xml:space="preserve">2408920</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4850,11 +4850,11 @@
         </is>
       </c>
       <c r="H81">
-        <v>999</v>
+        <v>754</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258737</t>
+          <t xml:space="preserve">311258825</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4891,17 +4891,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holløsevej 10C</t>
+          <t xml:space="preserve">Nytorv 14</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">4420</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2401302</t>
+          <t xml:space="preserve">2408839</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4910,16 +4910,16 @@
         </is>
       </c>
       <c r="H82">
-        <v>564</v>
+        <v>840</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258791</t>
+          <t xml:space="preserve">311264148</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-08-02</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -4951,17 +4951,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanevej 18E</t>
+          <t xml:space="preserve">Svinningehallen 1</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4520</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408920</t>
+          <t xml:space="preserve">719759, 2391621</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4970,16 +4970,16 @@
         </is>
       </c>
       <c r="H83">
-        <v>754</v>
+        <v>3125</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258825</t>
+          <t xml:space="preserve">311350102</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-09-05</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 40</t>
+          <t xml:space="preserve">Øvej 5A</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5021,25 +5021,25 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">9415784</t>
+          <t xml:space="preserve">2402709</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H84">
-        <v>1014</v>
+        <v>1724</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258739</t>
+          <t xml:space="preserve">311272027</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-09-11</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nytorv 14</t>
+          <t xml:space="preserve">Øvej 5B</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5081,25 +5081,25 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408839</t>
+          <t xml:space="preserve">2402709</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H85">
-        <v>840</v>
+        <v>346</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264148</t>
+          <t xml:space="preserve">311272304</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-02</t>
+          <t xml:space="preserve">2027-09-12</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5131,17 +5131,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svinningehallen 1</t>
+          <t xml:space="preserve">Markedspladsen 6A</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">4520</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">719759, 2391621</t>
+          <t xml:space="preserve">5334610</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5150,16 +5150,16 @@
         </is>
       </c>
       <c r="H86">
-        <v>3125</v>
+        <v>472</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311350102</t>
+          <t xml:space="preserve">311274663</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-05</t>
+          <t xml:space="preserve">2027-09-22</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øvej 5A</t>
+          <t xml:space="preserve">Sportsvej 2</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2402709</t>
+          <t xml:space="preserve">719772, 2409825</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5210,16 +5210,16 @@
         </is>
       </c>
       <c r="H87">
-        <v>1724</v>
+        <v>2306</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311272027</t>
+          <t xml:space="preserve">311276692</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-11</t>
+          <t xml:space="preserve">2027-10-04</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øvej 5B</t>
+          <t xml:space="preserve">Østergade 64</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5261,25 +5261,25 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2402709</t>
+          <t xml:space="preserve">2408814</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H88">
-        <v>346</v>
+        <v>459</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311272304</t>
+          <t xml:space="preserve">311276699</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-12</t>
+          <t xml:space="preserve">2027-10-04</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5311,35 +5311,35 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Markedspladsen 6A</t>
+          <t xml:space="preserve">Øvej 3</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">5334610</t>
+          <t xml:space="preserve">9415784</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H89">
-        <v>472</v>
+        <v>1030</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311274663</t>
+          <t xml:space="preserve">311276724</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-22</t>
+          <t xml:space="preserve">2027-10-04</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 64</t>
+          <t xml:space="preserve">Øvej 3</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5381,20 +5381,20 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408814</t>
+          <t xml:space="preserve">9415784</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H90">
-        <v>459</v>
+        <v>1350</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276699</t>
+          <t xml:space="preserve">311276724</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sportsvej 2</t>
+          <t xml:space="preserve">Øvej 3</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5441,20 +5441,20 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">719772, 2409825</t>
+          <t xml:space="preserve">9415784</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H91">
-        <v>2306</v>
+        <v>820</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276692</t>
+          <t xml:space="preserve">311276724</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5491,35 +5491,35 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øvej 3</t>
+          <t xml:space="preserve">Ledegårdsvej 15</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4520</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">9415784</t>
+          <t xml:space="preserve">2391684</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H92">
-        <v>1030</v>
+        <v>278</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276724</t>
+          <t xml:space="preserve">311281139</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-04</t>
+          <t xml:space="preserve">2027-10-30</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -5551,35 +5551,35 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øvej 3</t>
+          <t xml:space="preserve">Stormøllevej 9</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">9415784</t>
+          <t xml:space="preserve">5337399</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H93">
-        <v>1350</v>
+        <v>492</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276724</t>
+          <t xml:space="preserve">311282530</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-04</t>
+          <t xml:space="preserve">2027-11-07</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -5611,35 +5611,35 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øvej 3</t>
+          <t xml:space="preserve">Ved Faurgården 7</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">9415784</t>
+          <t xml:space="preserve">5340353</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H94">
-        <v>820</v>
+        <v>745</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276724</t>
+          <t xml:space="preserve">311282521</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-04</t>
+          <t xml:space="preserve">2027-11-07</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -5671,17 +5671,17 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ledegårdsvej 15</t>
+          <t xml:space="preserve">Industrivej 14B</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">4520</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2391684</t>
+          <t xml:space="preserve">2409959</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5690,16 +5690,16 @@
         </is>
       </c>
       <c r="H95">
-        <v>278</v>
+        <v>623</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311281139</t>
+          <t xml:space="preserve">311283082</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-30</t>
+          <t xml:space="preserve">2027-11-09</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -5731,17 +5731,17 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stormøllevej 9</t>
+          <t xml:space="preserve">Kirkevej 1</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4532</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">5337399</t>
+          <t xml:space="preserve">2384014</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5750,16 +5750,16 @@
         </is>
       </c>
       <c r="H96">
-        <v>492</v>
+        <v>264</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311282530</t>
+          <t xml:space="preserve">311283182</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-07</t>
+          <t xml:space="preserve">2027-11-09</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -5791,35 +5791,35 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Faurgården 7</t>
+          <t xml:space="preserve">Kirkevej 1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4532</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">5340353</t>
+          <t xml:space="preserve">2384014</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H97">
-        <v>745</v>
+        <v>400</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311282521</t>
+          <t xml:space="preserve">311283182</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-07</t>
+          <t xml:space="preserve">2027-11-09</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5866,11 +5866,11 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H98">
-        <v>264</v>
+        <v>553</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -5911,35 +5911,35 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 1</t>
+          <t xml:space="preserve">Ringstedvej 43A</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">4532</t>
+          <t xml:space="preserve">4440</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2384014</t>
+          <t xml:space="preserve">2390836</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H99">
-        <v>400</v>
+        <v>262</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283182</t>
+          <t xml:space="preserve">311283188</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-09</t>
+          <t xml:space="preserve">2027-11-10</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -5971,35 +5971,35 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 1</t>
+          <t xml:space="preserve">Skarridsøgade 37</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">4532</t>
+          <t xml:space="preserve">4450</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2384014</t>
+          <t xml:space="preserve">2388022</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H100">
-        <v>553</v>
+        <v>2632</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283182</t>
+          <t xml:space="preserve">311283186</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-09</t>
+          <t xml:space="preserve">2027-11-10</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6031,35 +6031,35 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej 14B</t>
+          <t xml:space="preserve">Skarridsøgade 37A</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4450</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2409959</t>
+          <t xml:space="preserve">2388022</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H101">
-        <v>623</v>
+        <v>528</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283082</t>
+          <t xml:space="preserve">311283186</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-09</t>
+          <t xml:space="preserve">2027-11-10</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6091,17 +6091,17 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skarridsøgade 37</t>
+          <t xml:space="preserve">Udbyvej 44</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2388022</t>
+          <t xml:space="preserve">2395636</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6110,16 +6110,16 @@
         </is>
       </c>
       <c r="H102">
-        <v>2632</v>
+        <v>396</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283186</t>
+          <t xml:space="preserve">311287525</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-10</t>
+          <t xml:space="preserve">2027-12-06</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6151,35 +6151,35 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skarridsøgade 37A</t>
+          <t xml:space="preserve">Udbyvej 42</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2388022</t>
+          <t xml:space="preserve">2395380</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H103">
-        <v>528</v>
+        <v>872</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283186</t>
+          <t xml:space="preserve">311287726</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-10</t>
+          <t xml:space="preserve">2027-12-07</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6211,35 +6211,35 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringstedvej 43A</t>
+          <t xml:space="preserve">Udbyvej 42</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">4440</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2390836</t>
+          <t xml:space="preserve">2395380</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H104">
-        <v>262</v>
+        <v>672</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311283188</t>
+          <t xml:space="preserve">311287726</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-10</t>
+          <t xml:space="preserve">2027-12-07</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udbyvej 44</t>
+          <t xml:space="preserve">Udbyvej 42</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6281,25 +6281,25 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2395636</t>
+          <t xml:space="preserve">2395380</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H105">
-        <v>396</v>
+        <v>330</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287525</t>
+          <t xml:space="preserve">311287726</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-06</t>
+          <t xml:space="preserve">2027-12-07</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6346,11 +6346,11 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H106">
-        <v>872</v>
+        <v>527</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udbyvej 42</t>
+          <t xml:space="preserve">Udby Kirkevej 21</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2395380</t>
+          <t xml:space="preserve">2395597</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -6410,16 +6410,16 @@
         </is>
       </c>
       <c r="H107">
-        <v>672</v>
+        <v>1691</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287726</t>
+          <t xml:space="preserve">311288089</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-07</t>
+          <t xml:space="preserve">2027-12-11</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udbyvej 42</t>
+          <t xml:space="preserve">Udby Kirkevej 23</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6461,25 +6461,25 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2395380</t>
+          <t xml:space="preserve">2395597</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H108">
-        <v>330</v>
+        <v>2066</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287726</t>
+          <t xml:space="preserve">311289980</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-07</t>
+          <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udbyvej 42</t>
+          <t xml:space="preserve">Vandtårnsvej 6</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -6521,25 +6521,25 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2395380</t>
+          <t xml:space="preserve">5339301</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H109">
-        <v>527</v>
+        <v>503</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287726</t>
+          <t xml:space="preserve">311295412</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-07</t>
+          <t xml:space="preserve">2028-01-31</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -6571,35 +6571,35 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udby Kirkevej 21</t>
+          <t xml:space="preserve">Lersøparken 142</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4390</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2395597</t>
+          <t xml:space="preserve">7416498</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H110">
-        <v>1691</v>
+        <v>606</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288089</t>
+          <t xml:space="preserve">311307671</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-11</t>
+          <t xml:space="preserve">2028-04-11</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -6631,17 +6631,17 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udby Kirkevej 23</t>
+          <t xml:space="preserve">Solvænget 1</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2395597</t>
+          <t xml:space="preserve">2408810</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -6650,16 +6650,16 @@
         </is>
       </c>
       <c r="H111">
-        <v>2066</v>
+        <v>275</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289980</t>
+          <t xml:space="preserve">311307633</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-21</t>
+          <t xml:space="preserve">2028-04-11</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -6691,35 +6691,35 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vandtårnsvej 6</t>
+          <t xml:space="preserve">Solvænget 11</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">5339301</t>
+          <t xml:space="preserve">2408810</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H112">
-        <v>503</v>
+        <v>275</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311295412</t>
+          <t xml:space="preserve">311307633</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-31</t>
+          <t xml:space="preserve">2028-04-11</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solvænget 1</t>
+          <t xml:space="preserve">Solvænget 6</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H113">
@@ -6811,35 +6811,35 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solvænget 6</t>
+          <t xml:space="preserve">Højgårdsvej 24</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4350</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408810</t>
+          <t xml:space="preserve">2410722, 100800374</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H114">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307633</t>
+          <t xml:space="preserve">311307933</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-11</t>
+          <t xml:space="preserve">2028-04-12</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -6871,35 +6871,35 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solvænget 11</t>
+          <t xml:space="preserve">Sofiesminde Alle 5</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408810</t>
+          <t xml:space="preserve">100011737</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H115">
-        <v>275</v>
+        <v>991</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307633</t>
+          <t xml:space="preserve">311308315</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-11</t>
+          <t xml:space="preserve">2028-04-13</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -6931,17 +6931,17 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lersøparken 142</t>
+          <t xml:space="preserve">Tjørnegården 1</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">4390</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">7416498</t>
+          <t xml:space="preserve">10055688</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -6950,16 +6950,16 @@
         </is>
       </c>
       <c r="H116">
-        <v>606</v>
+        <v>1354</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307671</t>
+          <t xml:space="preserve">311308295</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-11</t>
+          <t xml:space="preserve">2028-04-13</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -6991,35 +6991,35 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højgårdsvej 24</t>
+          <t xml:space="preserve">Havnevej 7</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">4350</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2410722, 100800374</t>
+          <t xml:space="preserve">5334808</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H117">
-        <v>262</v>
+        <v>1048</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311307933</t>
+          <t xml:space="preserve">311342403</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-12</t>
+          <t xml:space="preserve">2028-10-19</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sofiesminde Alle 5</t>
+          <t xml:space="preserve">Jernbanevej 29A</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">100011737</t>
+          <t xml:space="preserve">267924, 267925, 267926</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -7070,16 +7070,16 @@
         </is>
       </c>
       <c r="H118">
-        <v>991</v>
+        <v>600</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311308315</t>
+          <t xml:space="preserve">311352731</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-13</t>
+          <t xml:space="preserve">2028-12-20</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7111,17 +7111,17 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjørnegården 1</t>
+          <t xml:space="preserve">Søbæksvej 30</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4450</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">10055688</t>
+          <t xml:space="preserve">270575</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -7130,16 +7130,16 @@
         </is>
       </c>
       <c r="H119">
-        <v>1354</v>
+        <v>2562</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311308295</t>
+          <t xml:space="preserve">311354541</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-13</t>
+          <t xml:space="preserve">2029-01-14</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnevej 7</t>
+          <t xml:space="preserve">Omfartsvejen 27</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7181,25 +7181,25 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">5334808</t>
+          <t xml:space="preserve">8282784</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H120">
-        <v>1048</v>
+        <v>353</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311342403</t>
+          <t xml:space="preserve">311403255</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-19</t>
+          <t xml:space="preserve">2029-10-10</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omfartsvejen 27</t>
+          <t xml:space="preserve">Dampmøllevej 2</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">8282784</t>
+          <t xml:space="preserve">7380402</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -7250,16 +7250,16 @@
         </is>
       </c>
       <c r="H121">
-        <v>353</v>
+        <v>1944</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311403255</t>
+          <t xml:space="preserve">311448909</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-10</t>
+          <t xml:space="preserve">2030-07-09</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dampmøllevej 2</t>
+          <t xml:space="preserve">Finsings Plads 1</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7301,25 +7301,25 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">7380402</t>
+          <t xml:space="preserve">719742, 9386046</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H122">
-        <v>1944</v>
+        <v>339</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311448909</t>
+          <t xml:space="preserve">311464714</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-07-09</t>
+          <t xml:space="preserve">2030-10-01</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finsings Plads 1</t>
+          <t xml:space="preserve">Ladegårdsparken Vest 167</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7361,25 +7361,25 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">719742, 9386046</t>
+          <t xml:space="preserve">5339287</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H123">
-        <v>339</v>
+        <v>840</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311464714</t>
+          <t xml:space="preserve">311658138</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-01</t>
+          <t xml:space="preserve">2033-02-06</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -7411,17 +7411,17 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ladegårdsparken Vest 167</t>
+          <t xml:space="preserve">Skolevej 37</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4440</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">5339287</t>
+          <t xml:space="preserve">2389399</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -7430,16 +7430,16 @@
         </is>
       </c>
       <c r="H124">
-        <v>840</v>
+        <v>1723</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311658138</t>
+          <t xml:space="preserve">311735788</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-06</t>
+          <t xml:space="preserve">2034-01-26</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -7471,17 +7471,17 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 37</t>
+          <t xml:space="preserve">Skolevej 4</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">4440</t>
+          <t xml:space="preserve">4532</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2389399</t>
+          <t xml:space="preserve">2384021</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -7490,16 +7490,16 @@
         </is>
       </c>
       <c r="H125">
-        <v>1723</v>
+        <v>1872</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311735788</t>
+          <t xml:space="preserve">311834296</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-26</t>
+          <t xml:space="preserve">2035-05-26</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -7531,30 +7531,30 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vandtårnsvej 3</t>
+          <t xml:space="preserve">Skolevej 4</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4532</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">10056287</t>
+          <t xml:space="preserve">2384021</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H126">
-        <v>11883</v>
+        <v>4238</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311834297</t>
+          <t xml:space="preserve">311834295</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -7591,17 +7591,17 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 4</t>
+          <t xml:space="preserve">Vandtårnsvej 3</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">4532</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2384021</t>
+          <t xml:space="preserve">10056287</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -7610,11 +7610,11 @@
         </is>
       </c>
       <c r="H127">
-        <v>1872</v>
+        <v>11883</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311834296</t>
+          <t xml:space="preserve">311834297</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -7651,35 +7651,35 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 4</t>
+          <t xml:space="preserve">Bispehøjen 2</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">4532</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2384021</t>
+          <t xml:space="preserve">5338074</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H128">
-        <v>4238</v>
+        <v>1440</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311834295</t>
+          <t xml:space="preserve">311850583</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-26</t>
+          <t xml:space="preserve">2035-08-21</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -7726,15 +7726,15 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H129">
-        <v>1440</v>
+        <v>301</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311850583</t>
+          <t xml:space="preserve">311850586</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -7786,15 +7786,15 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H130">
-        <v>301</v>
+        <v>1440</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311850584</t>
+          <t xml:space="preserve">311850583</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -7846,11 +7846,11 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H131">
-        <v>1440</v>
+        <v>1963</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -7906,11 +7906,11 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H132">
-        <v>1963</v>
+        <v>477</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -7966,11 +7966,11 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H133">
-        <v>477</v>
+        <v>1685</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -8026,15 +8026,15 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H134">
-        <v>1685</v>
+        <v>2108</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311850583</t>
+          <t xml:space="preserve">311850588</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -8086,15 +8086,15 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H135">
-        <v>2108</v>
+        <v>1440</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311850584</t>
+          <t xml:space="preserve">311850583</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8131,35 +8131,35 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bispehøjen 2</t>
+          <t xml:space="preserve">Holbækvej 108</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4450</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">5338074</t>
+          <t xml:space="preserve">7226325</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H136">
-        <v>1440</v>
+        <v>1188</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311850583</t>
+          <t xml:space="preserve">311851447</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-21</t>
+          <t xml:space="preserve">2035-08-26</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -8206,15 +8206,15 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H137">
-        <v>1188</v>
+        <v>747</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851447</t>
+          <t xml:space="preserve">311851452</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -8266,15 +8266,15 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="H138">
-        <v>747</v>
+        <v>431</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851452</t>
+          <t xml:space="preserve">311851447</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -8326,11 +8326,11 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H139">
-        <v>431</v>
+        <v>2038</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
@@ -8386,11 +8386,11 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H140">
-        <v>2038</v>
+        <v>735</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H141">
@@ -8506,11 +8506,11 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H142">
-        <v>735</v>
+        <v>1010</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
@@ -8566,11 +8566,11 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H143">
-        <v>1010</v>
+        <v>385</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
@@ -8626,11 +8626,11 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H144">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
@@ -8671,35 +8671,35 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holbækvej 108</t>
+          <t xml:space="preserve">Hovedgaden 42</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450</t>
+          <t xml:space="preserve">4350</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">7226325</t>
+          <t xml:space="preserve">2410274</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H145">
-        <v>379</v>
+        <v>3739</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851447</t>
+          <t xml:space="preserve">311852051</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-26</t>
+          <t xml:space="preserve">2035-08-28</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -8741,20 +8741,20 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2410274</t>
+          <t xml:space="preserve">7564740</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H146">
-        <v>3739</v>
+        <v>640</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311852051</t>
+          <t xml:space="preserve">311852047</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -8851,35 +8851,35 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 42</t>
+          <t xml:space="preserve">Tølløsevej 64</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">4350</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">7564740</t>
+          <t xml:space="preserve">7376334</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H148">
-        <v>640</v>
+        <v>1242</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311852047</t>
+          <t xml:space="preserve">311852541</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-28</t>
+          <t xml:space="preserve">2035-08-29</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -8911,35 +8911,35 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tølløsevej 64</t>
+          <t xml:space="preserve">Anders Larsensvej 1</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">7376334</t>
+          <t xml:space="preserve">8285343</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H149">
-        <v>1242</v>
+        <v>1404</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311852541</t>
+          <t xml:space="preserve">311864985</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-29</t>
+          <t xml:space="preserve">2035-10-29</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vandtårnsvej 10</t>
+          <t xml:space="preserve">Anders Larsensvej 3</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5339264</t>
+          <t xml:space="preserve">8285343</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -8990,11 +8990,11 @@
         </is>
       </c>
       <c r="H150">
-        <v>2285</v>
+        <v>324</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865121</t>
+          <t xml:space="preserve">311864983</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Damvej 19B</t>
+          <t xml:space="preserve">Anders Larsensvej 5</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9041,20 +9041,20 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">719717, 2384607</t>
+          <t xml:space="preserve">8285343</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H151">
-        <v>1096</v>
+        <v>2398</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865044</t>
+          <t xml:space="preserve">311864985</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vandtårnsvej 14</t>
+          <t xml:space="preserve">Damvej 19B</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9101,20 +9101,20 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">8077972</t>
+          <t xml:space="preserve">719717, 2384607</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H152">
-        <v>280</v>
+        <v>1096</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865122</t>
+          <t xml:space="preserve">311865044</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -9151,7 +9151,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anders Larsensvej 3</t>
+          <t xml:space="preserve">Vandtårnsvej 10</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9161,7 +9161,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">8285343</t>
+          <t xml:space="preserve">5339264</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -9170,11 +9170,11 @@
         </is>
       </c>
       <c r="H153">
-        <v>324</v>
+        <v>2285</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311864983</t>
+          <t xml:space="preserve">311865119</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anders Larsensvej 5</t>
+          <t xml:space="preserve">Vandtårnsvej 14</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">8285343</t>
+          <t xml:space="preserve">8077972</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -9230,11 +9230,11 @@
         </is>
       </c>
       <c r="H154">
-        <v>2398</v>
+        <v>280</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311864985</t>
+          <t xml:space="preserve">311865122</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anders Larsensvej 1</t>
+          <t xml:space="preserve">Mellemvang 7</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9281,25 +9281,25 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">8285343</t>
+          <t xml:space="preserve">5340835</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H155">
-        <v>1404</v>
+        <v>283</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311864985</t>
+          <t xml:space="preserve">311865496</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-29</t>
+          <t xml:space="preserve">2035-10-30</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -9331,35 +9331,35 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mellemvang 7</t>
+          <t xml:space="preserve">Brøndevej 15</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4305</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">5340835</t>
+          <t xml:space="preserve">719735, 2395810</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H156">
-        <v>283</v>
+        <v>1542</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865496</t>
+          <t xml:space="preserve">311865658</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-30</t>
+          <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -9391,35 +9391,35 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brøndevej 15</t>
+          <t xml:space="preserve">Parallelvej 52</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">4305</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">719735, 2395810</t>
+          <t xml:space="preserve">5335410</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H157">
-        <v>1542</v>
+        <v>288</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865658</t>
+          <t xml:space="preserve">311866224</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-31</t>
+          <t xml:space="preserve">2035-11-04</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -9466,15 +9466,15 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H158">
-        <v>288</v>
+        <v>739</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866223</t>
+          <t xml:space="preserve">311866225</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -9526,15 +9526,15 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H159">
-        <v>739</v>
+        <v>640</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866223</t>
+          <t xml:space="preserve">311866227</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -9571,35 +9571,35 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallelvej 52</t>
+          <t xml:space="preserve">Skamstrupvej 18</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4440</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">5335410</t>
+          <t xml:space="preserve">2391265</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H160">
-        <v>640</v>
+        <v>1511</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866223</t>
+          <t xml:space="preserve">311866718</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-04</t>
+          <t xml:space="preserve">2035-11-06</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -9646,11 +9646,11 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H161">
-        <v>1511</v>
+        <v>1990</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -9706,11 +9706,11 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H162">
-        <v>1990</v>
+        <v>796</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -9766,11 +9766,11 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H163">
-        <v>796</v>
+        <v>836</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -9811,35 +9811,35 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skamstrupvej 18</t>
+          <t xml:space="preserve">Østergårdsvej 49</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t xml:space="preserve">4440</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2391265</t>
+          <t xml:space="preserve">2402461</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H164">
-        <v>836</v>
+        <v>1804</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866718</t>
+          <t xml:space="preserve">311867558</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-06</t>
+          <t xml:space="preserve">2035-11-11</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergårdsvej 49</t>
+          <t xml:space="preserve">Østergårdsvej 51A</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -9886,15 +9886,15 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H165">
-        <v>1804</v>
+        <v>280</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311867558</t>
+          <t xml:space="preserve">311867559</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergårdsvej 51A</t>
+          <t xml:space="preserve">Østergårdsvej 53A</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -9941,20 +9941,20 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2402461</t>
+          <t xml:space="preserve">8820316</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H166">
-        <v>280</v>
+        <v>729</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311867559</t>
+          <t xml:space="preserve">311867560</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -9991,35 +9991,35 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergårdsvej 53A</t>
+          <t xml:space="preserve">Bygaden 50</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4305</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">8820316</t>
+          <t xml:space="preserve">2395798</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H167">
-        <v>729</v>
+        <v>467</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311867560</t>
+          <t xml:space="preserve">311867756</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-11</t>
+          <t xml:space="preserve">2035-11-12</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 50</t>
+          <t xml:space="preserve">Orø Havn 3</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10061,25 +10061,25 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2395798</t>
+          <t xml:space="preserve">2395790</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H168">
-        <v>467</v>
+        <v>452</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311867756</t>
+          <t xml:space="preserve">311868836</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-12</t>
+          <t xml:space="preserve">2035-11-18</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -10111,17 +10111,17 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orø Havn 3</t>
+          <t xml:space="preserve">Krogvejen 4</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t xml:space="preserve">4305</t>
+          <t xml:space="preserve">4390</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2395790</t>
+          <t xml:space="preserve">2397479</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -10130,16 +10130,16 @@
         </is>
       </c>
       <c r="H169">
-        <v>452</v>
+        <v>427</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868836</t>
+          <t xml:space="preserve">311872573</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-18</t>
+          <t xml:space="preserve">2035-12-09</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -10186,11 +10186,11 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H170">
-        <v>427</v>
+        <v>645</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
@@ -10246,11 +10246,11 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H171">
-        <v>645</v>
+        <v>320</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
@@ -10306,11 +10306,11 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H172">
-        <v>320</v>
+        <v>1402</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
@@ -10366,15 +10366,15 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H173">
-        <v>1402</v>
+        <v>290</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872573</t>
+          <t xml:space="preserve">311872576</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -10411,35 +10411,35 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krogvejen 4</t>
+          <t xml:space="preserve">Gl Ringstedvej 32</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t xml:space="preserve">4390</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2397479</t>
+          <t xml:space="preserve">5339867</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H174">
-        <v>290</v>
+        <v>487</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872576</t>
+          <t xml:space="preserve">311874453</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-09</t>
+          <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -10471,30 +10471,30 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stestrupvej 41A</t>
+          <t xml:space="preserve">Gl Ringstedvej 32</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t xml:space="preserve">4360</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2400079, 100800056</t>
+          <t xml:space="preserve">5339867</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H175">
-        <v>1084</v>
+        <v>348</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874431</t>
+          <t xml:space="preserve">311874453</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -10531,30 +10531,30 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stestrupvej 41B</t>
+          <t xml:space="preserve">Gl Ringstedvej 32</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t xml:space="preserve">4360</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2400080, 100800076</t>
+          <t xml:space="preserve">5339867</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H176">
-        <v>1469</v>
+        <v>429</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874429</t>
+          <t xml:space="preserve">311874453</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -10606,11 +10606,11 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H177">
-        <v>487</v>
+        <v>396</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peder Billesvej 57</t>
+          <t xml:space="preserve">Gl Ringstedvej 32</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -10666,11 +10666,11 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H178">
-        <v>579</v>
+        <v>439</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
@@ -10726,11 +10726,11 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H179">
-        <v>348</v>
+        <v>396</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
@@ -10786,11 +10786,11 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H180">
-        <v>429</v>
+        <v>1293</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
@@ -10846,11 +10846,11 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H181">
-        <v>396</v>
+        <v>251</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Ringstedvej 32</t>
+          <t xml:space="preserve">Peder Billesvej 57</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -10906,11 +10906,11 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H182">
-        <v>439</v>
+        <v>579</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
@@ -10951,30 +10951,30 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Ringstedvej 32</t>
+          <t xml:space="preserve">Stestrupvej 41A</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4360</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">5339867</t>
+          <t xml:space="preserve">2400079, 100800056</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H183">
-        <v>396</v>
+        <v>1084</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874453</t>
+          <t xml:space="preserve">311874431</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -11011,30 +11011,30 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Ringstedvej 32</t>
+          <t xml:space="preserve">Stestrupvej 41B</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4360</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">5339867</t>
+          <t xml:space="preserve">2400080, 100800076</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H184">
-        <v>1293</v>
+        <v>1469</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874453</t>
+          <t xml:space="preserve">311874429</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Ringstedvej 32</t>
+          <t xml:space="preserve">Hesseløvej 12</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -11081,25 +11081,25 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">5339867</t>
+          <t xml:space="preserve">7153439</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H185">
-        <v>251</v>
+        <v>960</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874453</t>
+          <t xml:space="preserve">311875725</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-19</t>
+          <t xml:space="preserve">2036-01-08</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -11131,7 +11131,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hesseløvej 12</t>
+          <t xml:space="preserve">Kalvemosevej 1</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11141,25 +11141,25 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">7153439</t>
+          <t xml:space="preserve">100459791</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H186">
-        <v>960</v>
+        <v>379</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875725</t>
+          <t xml:space="preserve">311880095</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-08</t>
+          <t xml:space="preserve">2036-02-03</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -11191,35 +11191,35 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalvemosevej 1</t>
+          <t xml:space="preserve">Hovedgaden 36A</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4420</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">100459791</t>
+          <t xml:space="preserve">2402019</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H187">
-        <v>379</v>
+        <v>348</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311880095</t>
+          <t xml:space="preserve">311882274</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-03</t>
+          <t xml:space="preserve">2036-02-16</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -11261,20 +11261,20 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2402019</t>
+          <t xml:space="preserve">2402027</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H188">
-        <v>348</v>
+        <v>879</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311882274</t>
+          <t xml:space="preserve">311882268</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -11326,15 +11326,15 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H189">
-        <v>879</v>
+        <v>348</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311882271</t>
+          <t xml:space="preserve">311882275</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -11371,7 +11371,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 36A</t>
+          <t xml:space="preserve">Hovedgaden 36B</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -11381,20 +11381,20 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2402027</t>
+          <t xml:space="preserve">2402030</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H190">
-        <v>348</v>
+        <v>445</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311882271</t>
+          <t xml:space="preserve">311882265</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -11446,15 +11446,15 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H191">
-        <v>445</v>
+        <v>592</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311882265</t>
+          <t xml:space="preserve">311882266</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -11491,35 +11491,35 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 36B</t>
+          <t xml:space="preserve">Kalvemosevej 3</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t xml:space="preserve">4420</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2402030</t>
+          <t xml:space="preserve">5340919</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H192">
-        <v>592</v>
+        <v>345</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311882266</t>
+          <t xml:space="preserve">311882720</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-16</t>
+          <t xml:space="preserve">2036-02-18</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -11566,11 +11566,11 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H193">
-        <v>345</v>
+        <v>640</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
@@ -11611,35 +11611,35 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalvemosevej 3</t>
+          <t xml:space="preserve">Stestrupvej 49</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4360</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">5340919</t>
+          <t xml:space="preserve">8921449</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H194">
-        <v>640</v>
+        <v>3302</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311882720</t>
+          <t xml:space="preserve">311888237</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-18</t>
+          <t xml:space="preserve">2036-03-18</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -11686,15 +11686,15 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H195">
-        <v>3302</v>
+        <v>455</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888237</t>
+          <t xml:space="preserve">311888240</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -11731,35 +11731,35 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stestrupvej 49</t>
+          <t xml:space="preserve">Holbækvej 36</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t xml:space="preserve">4360</t>
+          <t xml:space="preserve">4370</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">8921449</t>
+          <t xml:space="preserve">9167622</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H196">
-        <v>455</v>
+        <v>1082</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888266</t>
+          <t xml:space="preserve">311893637</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-18</t>
+          <t xml:space="preserve">2036-04-13</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -11791,35 +11791,35 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holbækvej 36</t>
+          <t xml:space="preserve">Bøgen 1</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t xml:space="preserve">4370</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">9167622</t>
+          <t xml:space="preserve">719732, 5336412</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H197">
-        <v>1082</v>
+        <v>632</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311893637</t>
+          <t xml:space="preserve">311898603</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-13</t>
+          <t xml:space="preserve">2036-05-04</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -11851,35 +11851,35 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bøgen 1</t>
+          <t xml:space="preserve">Holbækvej 30C</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4370</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">719732, 5336412</t>
+          <t xml:space="preserve">2408102</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H198">
-        <v>632</v>
+        <v>1080</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311898603</t>
+          <t xml:space="preserve">311904052</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-04</t>
+          <t xml:space="preserve">2036-05-27</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -11911,30 +11911,30 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 74</t>
+          <t xml:space="preserve">Holbækvej 34</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t xml:space="preserve">4520</t>
+          <t xml:space="preserve">4370</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2391620</t>
+          <t xml:space="preserve">719778, 2408102</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H199">
-        <v>722</v>
+        <v>2048</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903997</t>
+          <t xml:space="preserve">311904037</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -11986,15 +11986,15 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H200">
-        <v>640</v>
+        <v>722</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903995</t>
+          <t xml:space="preserve">311903997</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -12031,7 +12031,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 76F</t>
+          <t xml:space="preserve">Hovedgaden 74</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -12046,11 +12046,11 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H201">
-        <v>441</v>
+        <v>640</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
@@ -12106,11 +12106,11 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H202">
-        <v>654</v>
+        <v>441</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
@@ -12166,11 +12166,11 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H203">
-        <v>4699</v>
+        <v>654</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
@@ -12226,11 +12226,11 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H204">
-        <v>622</v>
+        <v>4699</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
@@ -12271,30 +12271,30 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holbækvej 30C</t>
+          <t xml:space="preserve">Hovedgaden 76F</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t xml:space="preserve">4370</t>
+          <t xml:space="preserve">4520</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408102</t>
+          <t xml:space="preserve">2391620</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H205">
-        <v>1080</v>
+        <v>622</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311904052</t>
+          <t xml:space="preserve">311903995</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -12331,7 +12331,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hybenvang 63</t>
+          <t xml:space="preserve">Hybenvang 61A</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">5340689</t>
+          <t xml:space="preserve">265333, 265334</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -12350,11 +12350,11 @@
         </is>
       </c>
       <c r="H206">
-        <v>634</v>
+        <v>418</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311904029</t>
+          <t xml:space="preserve">311904008</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -12391,30 +12391,30 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holbækvej 34</t>
+          <t xml:space="preserve">Hybenvang 63</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t xml:space="preserve">4370</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">719778, 2408102</t>
+          <t xml:space="preserve">5340689</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H207">
-        <v>2048</v>
+        <v>634</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311904037</t>
+          <t xml:space="preserve">311904029</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -12751,7 +12751,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torpet 1</t>
+          <t xml:space="preserve">Kasernevej 43</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -12761,20 +12761,20 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">10218277</t>
+          <t xml:space="preserve">7095821</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H213">
-        <v>1088</v>
+        <v>802</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911479</t>
+          <t xml:space="preserve">311911471</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -12826,15 +12826,15 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H214">
-        <v>802</v>
+        <v>1348</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911471</t>
+          <t xml:space="preserve">311911474</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -12871,7 +12871,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kasernevej 43</t>
+          <t xml:space="preserve">Torpet 1</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -12881,20 +12881,20 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">7095821</t>
+          <t xml:space="preserve">10218277</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H215">
-        <v>1348</v>
+        <v>1088</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911466</t>
+          <t xml:space="preserve">311911479</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -12954,7 +12954,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911823</t>
+          <t xml:space="preserve">311911830</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -13111,30 +13111,30 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuse Byvej 16</t>
+          <t xml:space="preserve">Sportsvej 3</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2393534</t>
+          <t xml:space="preserve">7376333</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H219">
-        <v>2664</v>
+        <v>2665</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311912618</t>
+          <t xml:space="preserve">311912624</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -13171,30 +13171,30 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuse Byvej 16</t>
+          <t xml:space="preserve">Sportsvej 3</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t xml:space="preserve">4300</t>
+          <t xml:space="preserve">4340</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2393534</t>
+          <t xml:space="preserve">7376333</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H220">
-        <v>673</v>
+        <v>2066</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311912618</t>
+          <t xml:space="preserve">311912624</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -13246,11 +13246,11 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H221">
-        <v>2665</v>
+        <v>1115</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
@@ -13306,11 +13306,11 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H222">
-        <v>2066</v>
+        <v>466</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
@@ -13351,7 +13351,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sportsvej 3</t>
+          <t xml:space="preserve">Sportsvej 5</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -13366,11 +13366,11 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H223">
-        <v>1115</v>
+        <v>352</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
@@ -13411,30 +13411,30 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sportsvej 5</t>
+          <t xml:space="preserve">Tuse Byvej 16</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t xml:space="preserve">7376333</t>
+          <t xml:space="preserve">2393534</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H224">
-        <v>352</v>
+        <v>2664</v>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311912624</t>
+          <t xml:space="preserve">311912618</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -13471,30 +13471,30 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sportsvej 3</t>
+          <t xml:space="preserve">Tuse Byvej 16</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340</t>
+          <t xml:space="preserve">4300</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t xml:space="preserve">7376333</t>
+          <t xml:space="preserve">2393534</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H225">
-        <v>466</v>
+        <v>673</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311912624</t>
+          <t xml:space="preserve">311912618</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -13831,7 +13831,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovlystvej 2</t>
+          <t xml:space="preserve">Ellebjergvej 31A</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -13841,20 +13841,20 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2386579</t>
+          <t xml:space="preserve">2387969</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H231">
-        <v>1668</v>
+        <v>297</v>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311919644</t>
+          <t xml:space="preserve">311919655</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -13891,7 +13891,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ellebjergvej 31A</t>
+          <t xml:space="preserve">Skovlystvej 2</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -13901,20 +13901,20 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2387969</t>
+          <t xml:space="preserve">2386579</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H232">
-        <v>297</v>
+        <v>1668</v>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311919655</t>
+          <t xml:space="preserve">311919644</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuse Byvej 8</t>
+          <t xml:space="preserve">Tuse Byvej 2</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -13961,20 +13961,20 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2393535</t>
+          <t xml:space="preserve">2393546</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H233">
-        <v>308</v>
+        <v>7356</v>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311919722</t>
+          <t xml:space="preserve">311919716</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -14026,11 +14026,11 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H234">
-        <v>7356</v>
+        <v>355</v>
       </c>
       <c r="I234" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuse Byvej 2</t>
+          <t xml:space="preserve">Tuse Byvej 8</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -14081,20 +14081,20 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2393546</t>
+          <t xml:space="preserve">2393535</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H235">
-        <v>355</v>
+        <v>308</v>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311919716</t>
+          <t xml:space="preserve">311919722</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">

--- a/public/exports/29189447.xlsx
+++ b/public/exports/29189447.xlsx
@@ -9414,7 +9414,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866224</t>
+          <t xml:space="preserve">311866223</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">

--- a/public/exports/29189447.xlsx
+++ b/public/exports/29189447.xlsx
@@ -1674,7 +1674,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">200042618</t>
+          <t xml:space="preserve">200042636</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311850583</t>
+          <t xml:space="preserve">311850584</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311850586</t>
+          <t xml:space="preserve">311850584</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -7794,7 +7794,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311850583</t>
+          <t xml:space="preserve">311850584</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311850583</t>
+          <t xml:space="preserve">311850584</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311850583</t>
+          <t xml:space="preserve">311850584</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -7974,7 +7974,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311850583</t>
+          <t xml:space="preserve">311850584</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311850588</t>
+          <t xml:space="preserve">311850584</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311850583</t>
+          <t xml:space="preserve">311850584</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865119</t>
+          <t xml:space="preserve">311865121</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866225</t>
+          <t xml:space="preserve">311866223</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866227</t>
+          <t xml:space="preserve">311866223</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311882268</t>
+          <t xml:space="preserve">311882271</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -11334,7 +11334,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311882275</t>
+          <t xml:space="preserve">311882271</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -11694,7 +11694,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888240</t>
+          <t xml:space="preserve">311888266</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -12954,7 +12954,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911830</t>
+          <t xml:space="preserve">311911823</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">

--- a/public/exports/29189447.xlsx
+++ b/public/exports/29189447.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L237"/>
+  <dimension ref="A1:M237"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -904,10 +974,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -964,10 +1039,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1024,10 +1104,15 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1084,10 +1169,15 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1144,10 +1234,15 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1204,10 +1299,15 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1264,10 +1364,15 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1324,10 +1429,15 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1384,10 +1494,15 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1444,10 +1559,15 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1504,10 +1624,15 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1559,15 +1684,20 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-17</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1619,15 +1749,20 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-05-25</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1674,20 +1809,25 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">200042636</t>
+          <t xml:space="preserve">200042632</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-12-08</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1739,15 +1879,20 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-03-21</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1799,15 +1944,20 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-20</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1859,15 +2009,20 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1919,15 +2074,20 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1979,15 +2139,20 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-29</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2039,15 +2204,20 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-29</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2099,15 +2269,20 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-29</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2159,15 +2334,20 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-29</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2219,15 +2399,20 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-02</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2279,15 +2464,20 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-02</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2339,15 +2529,20 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-04</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2399,15 +2594,20 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-13</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2459,15 +2659,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t xml:space="preserve">John Klysner Consult ApS</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-30</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2519,15 +2724,20 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-02-21</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2579,15 +2789,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-09</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2639,15 +2854,20 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-13</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2699,15 +2919,20 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-13</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2759,15 +2984,20 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-15</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2819,15 +3049,20 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-15</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2879,15 +3114,20 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-15</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2939,15 +3179,20 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-15</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2999,15 +3244,20 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-15</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3059,15 +3309,20 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-15</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3119,15 +3374,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-15</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3179,15 +3439,20 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-24</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3239,15 +3504,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-24</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3299,15 +3569,20 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-24</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3359,15 +3634,20 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-24</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3419,15 +3699,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-24</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3479,15 +3764,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-30</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-06</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3599,15 +3894,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-06</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3659,15 +3959,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-06</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3719,15 +4024,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-25</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3779,15 +4089,20 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-26</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3839,15 +4154,20 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-26</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3899,15 +4219,20 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t xml:space="preserve">ARI Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-26</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3959,15 +4284,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-26</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-23</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4199,15 +4544,20 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-29</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4259,15 +4609,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-31</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4319,15 +4674,20 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-01</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4379,15 +4739,20 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-01</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4439,15 +4804,20 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-01</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4499,15 +4869,20 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-01</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4559,15 +4934,20 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-06</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4619,15 +4999,20 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-06</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4679,15 +5064,20 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4739,15 +5129,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4799,15 +5194,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4859,15 +5259,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4919,15 +5324,20 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-02</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4979,15 +5389,20 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-05</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5039,15 +5454,20 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-11</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5099,15 +5519,20 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-12</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5159,15 +5584,20 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-22</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5219,15 +5649,20 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-04</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5279,15 +5714,20 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-04</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5339,15 +5779,20 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-04</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5399,15 +5844,20 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-04</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5459,15 +5909,20 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-04</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5519,15 +5974,20 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-30</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5579,15 +6039,20 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-07</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5639,15 +6104,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-07</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5699,15 +6169,20 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-09</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5759,15 +6234,20 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-09</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5819,15 +6299,20 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-09</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5879,15 +6364,20 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-09</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5939,15 +6429,20 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-10</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5999,15 +6494,20 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-10</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6059,15 +6559,20 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-10</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6119,15 +6624,20 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-06</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6179,15 +6689,20 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-07</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6239,15 +6754,20 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-07</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6299,15 +6819,20 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-07</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6359,15 +6884,20 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-07</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6419,15 +6949,20 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-11</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6479,15 +7014,20 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6539,15 +7079,20 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-31</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6599,15 +7144,20 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-04-11</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6659,15 +7209,20 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-04-11</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6719,15 +7274,20 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-04-11</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6779,15 +7339,20 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-04-11</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6839,15 +7404,20 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-04-12</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6899,15 +7469,20 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-04-13</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6959,15 +7534,20 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-04-13</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7019,15 +7599,20 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-10-19</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7079,15 +7664,20 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-12-20</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7139,15 +7729,20 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-01-14</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7199,15 +7794,20 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-10-10</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7259,15 +7859,20 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
+          <t xml:space="preserve">AURA Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-07-09</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7319,15 +7924,20 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-01</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7379,15 +7989,20 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-06</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7439,15 +8054,20 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
+          <t xml:space="preserve">ISOLINK ApS</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-01-26</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7499,15 +8119,20 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-26</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7559,15 +8184,20 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-26</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7619,15 +8249,20 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-26</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7674,20 +8309,25 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311850584</t>
+          <t xml:space="preserve">311850583</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-21</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7739,15 +8379,20 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-21</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7794,20 +8439,25 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311850584</t>
+          <t xml:space="preserve">311850583</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-21</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7854,20 +8504,25 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311850584</t>
+          <t xml:space="preserve">311850583</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-21</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7914,20 +8569,25 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311850584</t>
+          <t xml:space="preserve">311850583</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-21</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7974,20 +8634,25 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311850584</t>
+          <t xml:space="preserve">311850583</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-21</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8039,15 +8704,20 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-21</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8094,20 +8764,25 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311850584</t>
+          <t xml:space="preserve">311850583</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-21</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8159,15 +8834,20 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-26</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8219,15 +8899,20 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-26</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8279,15 +8964,20 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-26</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8339,15 +9029,20 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-26</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8399,15 +9094,20 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-26</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8459,15 +9159,20 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-26</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8519,15 +9224,20 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-26</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8579,15 +9289,20 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-26</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8639,15 +9354,20 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-26</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8699,15 +9419,20 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-28</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8759,15 +9484,20 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-28</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8819,15 +9549,20 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-28</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8879,15 +9614,20 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-29</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8939,15 +9679,20 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-29</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8999,15 +9744,20 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-29</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9059,15 +9809,20 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-29</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9114,20 +9869,25 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865044</t>
+          <t xml:space="preserve">311865046</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-29</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9174,20 +9934,25 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865121</t>
+          <t xml:space="preserve">311865119</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-29</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9239,15 +10004,20 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-29</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9299,15 +10069,20 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-30</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9359,15 +10134,20 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9414,20 +10194,25 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866223</t>
+          <t xml:space="preserve">311866224</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-04</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9474,20 +10259,25 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866223</t>
+          <t xml:space="preserve">311866224</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-04</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9534,20 +10324,25 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866223</t>
+          <t xml:space="preserve">311866224</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-04</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9599,15 +10394,20 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-06</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9659,15 +10459,20 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-06</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9719,15 +10524,20 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-06</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9779,15 +10589,20 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-06</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9839,15 +10654,20 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-11</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9899,15 +10719,20 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-11</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9959,15 +10784,20 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-11</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10019,15 +10849,20 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-12</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10079,15 +10914,20 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-18</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10139,15 +10979,20 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-09</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10199,15 +11044,20 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-09</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10259,15 +11109,20 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-09</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10319,15 +11174,20 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-09</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10379,15 +11239,20 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-09</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10439,15 +11304,20 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10499,15 +11369,20 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10559,15 +11434,20 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10619,15 +11499,20 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10679,15 +11564,20 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10739,15 +11629,20 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10799,15 +11694,20 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10859,15 +11759,20 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10919,15 +11824,20 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10979,15 +11889,20 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11034,20 +11949,25 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874429</t>
+          <t xml:space="preserve">311874432</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11099,15 +12019,20 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-08</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11159,15 +12084,20 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-03</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11219,15 +12149,20 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-16</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11274,20 +12209,25 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311882271</t>
+          <t xml:space="preserve">311882268</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-16</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11334,20 +12274,25 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311882271</t>
+          <t xml:space="preserve">311882269</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-16</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11399,15 +12344,20 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-16</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11459,15 +12409,20 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-16</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11519,15 +12474,20 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-18</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11579,15 +12539,20 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-18</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11639,15 +12604,20 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-18</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11699,15 +12669,20 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-18</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11759,15 +12734,20 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-13</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11819,15 +12799,20 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-04</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11879,15 +12864,20 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-27</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11939,15 +12929,20 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-27</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11999,15 +12994,20 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-27</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12059,15 +13059,20 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-27</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12119,15 +13124,20 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-27</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12179,15 +13189,20 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-27</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12239,15 +13254,20 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-27</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12299,15 +13319,20 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-27</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12359,15 +13384,20 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-27</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12419,15 +13449,20 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-05-27</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12479,15 +13514,20 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-04</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12539,15 +13579,20 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-04</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12599,15 +13644,20 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-19</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12659,15 +13709,20 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-19</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12719,15 +13774,20 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-25</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12774,20 +13834,25 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911471</t>
+          <t xml:space="preserve">311911466</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-29</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12834,20 +13899,25 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911474</t>
+          <t xml:space="preserve">311911466</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-29</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12899,15 +13969,20 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-29</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12959,15 +14034,20 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-30</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13019,15 +14099,20 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-30</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13079,15 +14164,20 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-30</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13139,15 +14229,20 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-03</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13199,15 +14294,20 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-03</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13259,15 +14359,20 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-03</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13319,15 +14424,20 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-03</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13379,15 +14489,20 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-03</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13439,15 +14554,20 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-03</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13499,15 +14619,20 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-03</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13559,15 +14684,20 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-29</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13619,15 +14749,20 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-29</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13679,15 +14814,20 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-29</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13739,15 +14879,20 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-29</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13799,15 +14944,20 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-04</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13859,15 +15009,20 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-17</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13919,15 +15074,20 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-17</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13979,15 +15139,20 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-17</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14039,15 +15204,20 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-17</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14099,15 +15269,20 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-17</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14159,15 +15334,20 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-21</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14219,21 +15399,26 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-25</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L237" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L237"/>
+  <autoFilter ref="A1:M237"/>
 </worksheet>
 </file>
--- a/public/exports/29189447.xlsx
+++ b/public/exports/29189447.xlsx
@@ -1809,7 +1809,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">200042632</t>
+          <t xml:space="preserve">200042618</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865046</t>
+          <t xml:space="preserve">311865044</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -10194,7 +10194,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866224</t>
+          <t xml:space="preserve">311866223</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866224</t>
+          <t xml:space="preserve">311866223</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -10324,7 +10324,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866224</t>
+          <t xml:space="preserve">311866223</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874432</t>
+          <t xml:space="preserve">311874429</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888266</t>
+          <t xml:space="preserve">311888240</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CB Group ApS</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911826</t>
+          <t xml:space="preserve">311911823</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t xml:space="preserve">CB Group ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K217" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311911826</t>
+          <t xml:space="preserve">311911823</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t xml:space="preserve">CB Group ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K218" t="inlineStr">
